--- a/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
+++ b/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
@@ -18,17 +18,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Painel" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core_vs_Pack" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MUN_Assets" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peso_Assets" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Teste" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personagens_Campanha" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC_Mecanicas" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protagonistas" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses_Fases" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Faccoes" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mundo_Biomas" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conteudo_Futuro" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Divergencias" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core_vs_Pack" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MUN_Assets" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peso_Assets" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Teste" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personagens_Campanha" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC_Mecanicas" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protagonistas" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses_Fases" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Faccoes" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mundo_Biomas" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conteudo_Futuro" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -347,8 +348,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="PainelFocoTable" displayName="PainelFocoTable" ref="A17:D22" headerRowCount="1">
-  <autoFilter ref="A17:D22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="PainelFocoTable" displayName="PainelFocoTable" ref="A17:D23" headerRowCount="1">
+  <autoFilter ref="A17:D23"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Sinal"/>
     <tableColumn id="2" name="Objetivo"/>
@@ -386,7 +387,25 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="CorePackTable" displayName="CorePackTable" ref="A4:F12" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="DivergenciasTable" displayName="DivergenciasTable" ref="A4:I11" headerRowCount="1">
+  <autoFilter ref="A4:I11"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Status"/>
+    <tableColumn id="2" name="Tipo"/>
+    <tableColumn id="3" name="Personagem"/>
+    <tableColumn id="4" name="Nome no app"/>
+    <tableColumn id="5" name="Nome/pasta lore"/>
+    <tableColumn id="6" name="Faccao/Pasta"/>
+    <tableColumn id="7" name="Detalhe"/>
+    <tableColumn id="8" name="Acao sugerida"/>
+    <tableColumn id="9" name="Fonte"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="CorePackTable" displayName="CorePackTable" ref="A4:F12" headerRowCount="1">
   <autoFilter ref="A4:F12"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Bloco"/>
@@ -400,8 +419,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="MunAssetsTable" displayName="MunAssetsTable" ref="A4:J127" headerRowCount="1">
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="MunAssetsTable" displayName="MunAssetsTable" ref="A4:J127" headerRowCount="1">
   <autoFilter ref="A4:J127"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ID"/>
@@ -419,8 +438,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="HeavyOriginalsTable" displayName="HeavyOriginalsTable" ref="A4:G84" headerRowCount="1">
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="HeavyOriginalsTable" displayName="HeavyOriginalsTable" ref="A4:G84" headerRowCount="1">
   <autoFilter ref="A4:G84"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Original"/>
@@ -435,8 +454,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="ChecklistTable" displayName="ChecklistTable" ref="A4:F14" headerRowCount="1">
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="ChecklistTable" displayName="ChecklistTable" ref="A4:F14" headerRowCount="1">
   <autoFilter ref="A4:F14"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Prioridade"/>
@@ -450,8 +469,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="CampaignCharactersTable" displayName="CampaignCharactersTable" ref="A4:L55" headerRowCount="1">
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="CampaignCharactersTable" displayName="CampaignCharactersTable" ref="A4:L55" headerRowCount="1">
   <autoFilter ref="A4:L55"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Status"/>
@@ -471,8 +490,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="NpcMechanicsTable" displayName="NpcMechanicsTable" ref="A4:X55" headerRowCount="1">
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="NpcMechanicsTable" displayName="NpcMechanicsTable" ref="A4:X55" headerRowCount="1">
   <autoFilter ref="A4:X55"/>
   <tableColumns count="24">
     <tableColumn id="1" name="Status"/>
@@ -504,8 +523,18 @@
 </table>
 </file>
 
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="ProtagonistasTable" displayName="ProtagonistasTable" ref="A4:O11" headerRowCount="1">
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ControleRegrasTable" displayName="ControleRegrasTable" ref="G13:G18" headerRowCount="1">
+  <autoFilter ref="G13:G18"/>
+  <tableColumns count="1">
+    <tableColumn id="7" name="Regra"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="ProtagonistasTable" displayName="ProtagonistasTable" ref="A4:O11" headerRowCount="1">
   <autoFilter ref="A4:O11"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Status"/>
@@ -528,18 +557,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ControleRegrasTable" displayName="ControleRegrasTable" ref="G13:G18" headerRowCount="1">
-  <autoFilter ref="G13:G18"/>
-  <tableColumns count="1">
-    <tableColumn id="7" name="Regra"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="BossesFasesTable" displayName="BossesFasesTable" ref="A4:O19" headerRowCount="1">
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="BossesFasesTable" displayName="BossesFasesTable" ref="A4:O19" headerRowCount="1">
   <autoFilter ref="A4:O19"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Status"/>
@@ -562,8 +581,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="FaccoesTable" displayName="FaccoesTable" ref="A4:M10" headerRowCount="1">
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="FaccoesTable" displayName="FaccoesTable" ref="A4:M10" headerRowCount="1">
   <autoFilter ref="A4:M10"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Status"/>
@@ -584,8 +603,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="MundoBiomasTable" displayName="MundoBiomasTable" ref="A4:N12" headerRowCount="1">
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="MundoBiomasTable" displayName="MundoBiomasTable" ref="A4:N12" headerRowCount="1">
   <autoFilter ref="A4:N12"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Status"/>
@@ -607,8 +626,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="FutureContentTable" displayName="FutureContentTable" ref="A4:G10" headerRowCount="1">
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="FutureContentTable" displayName="FutureContentTable" ref="A4:G10" headerRowCount="1">
   <autoFilter ref="A4:G10"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Sistema"/>
@@ -2048,6 +2067,424 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="61" customWidth="1" min="7" max="7"/>
+    <col width="61" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Divergencias De Fonte App x Lore</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="19" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Use esta aba para resolver confusoes de nome, pasta, arquivo vazio e lore que ainda nao entrou no app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Personagem</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Nome no app</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Nome/pasta lore</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Faccao/Pasta</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Detalhe</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Acao sugerida</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Nome divergente</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Sélian Velan</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Sélian Velan</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Sélian</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Vila do Conhecimento Absorvido</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Vinculo aceito por nome parcial; conferir se e apelido/erro de grafia intencional.</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Padronizar nome no app ou registrar alias aprovado para nao confundir com outro NPC.</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>(D) Villa (Planicie) (Protagonistas)/Sélian (Protagonista Kairos ; Kuster)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Lore reconstruida do app</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Yor</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Yor</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Yor</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Ordem do Véu Cinza</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A ficha foi reconstruida a partir do workspace do app, nao de um arquivo original antigo.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Revisar com o mestre quando houver tempo e decidir se vira fonte definitiva.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>(C) Detetives (Véu cinzento)(.)/Yor (Yor Spy family)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Nome divergente</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Liryssa</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Liryssa</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Lyrissa</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Companhia da Maré Livre</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Vinculo aceito por alias nome; conferir se e apelido/erro de grafia intencional.</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Padronizar nome no app ou registrar alias aprovado para nao confundir com outro NPC.</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>(E) Aventureiros Maré (Mar)/Lyrissa (Capitã)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Lore reconstruida do app</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Varden</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Varden</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Varden</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Companhia da Maré Livre</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A ficha foi reconstruida a partir do workspace do app, nao de um arquivo original antigo.</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar com o mestre quando houver tempo e decidir se vira fonte definitiva.</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>(E) Aventureiros Maré (Mar)/Varden (Frankstain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Lore reconstruida do app</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Bront</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Bront</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Bront</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Companhia da Maré Livre</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>A ficha foi reconstruida a partir do workspace do app, nao de um arquivo original antigo.</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Revisar com o mestre quando houver tempo e decidir se vira fonte definitiva.</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>(E) Aventureiros Maré (Mar)/Bront (Cozinheiro Naval)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Nome divergente</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Maira Velan</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Maira Velan</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Maira</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Vila do Conhecimento Absorvido</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Vinculo aceito por nome parcial; conferir se e apelido/erro de grafia intencional.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Padronizar nome no app ou registrar alias aprovado para nao confundir com outro NPC.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>(D) Villa (Planicie) (Protagonistas)/Maira (Mãe de Sélian)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>APP sem pasta lore</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Ordem do Vazio Sereno</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Personagem existe no app, mas nenhuma pasta/arquivo de lore foi vinculado.</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Criar/vincular pasta em 01_LORE ou marcar conscientemente como somente-app.</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\danie\AppData\Roaming\FUSHI\workspace.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2373,7 +2810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8868,7 +9305,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11429,7 +11866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11824,7 +12261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15081,7 +15518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20580,7 +21017,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21177,1140 +21614,6 @@
       <c r="O11" s="8" t="inlineStr">
         <is>
           <t>character-dc758c81-53f2-4cea-953e-ee205f8586a2</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="51" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bosses, Cataclisma E Fichas Avancadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="19" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Planejamento de entidades com fases, mapas, aparencias, VFX/3D, interludios e controle de estado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Personagem</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Classe ficha</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Faccao</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Historia app</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Lore arquivo</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Eventos</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Fases</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Mapas</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>Img</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>Video</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Dominio/VFX</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>Controle necessario</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>Lore path</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - boss cataclisma</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Yanzik</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>BOSS CATACLISMA</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>FUSHI Escuro</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Viajante</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="11" t="inlineStr">
-        <is>
-          <t>requer VFX</t>
-        </is>
-      </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
-        </is>
-      </c>
-      <c r="O5" s="8" t="inlineStr">
-        <is>
-          <t>(B) FUSHI escuro (Andarilho)(.)/Yanzik (Guts)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - boss cataclisma</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Seraph</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>BOSS CATACLISMA</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>FUSHI Escuro</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Andarilho</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>requer VFX</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr">
-        <is>
-          <t>(B) FUSHI escuro (Andarilho)(.)/Seraph (Griffith)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - boss cataclisma</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Ryoku</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>BOSS CATACLISMA</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>FUSHI Escuro</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Ruinas</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>107</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="inlineStr">
-        <is>
-          <t>requer VFX</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
-        </is>
-      </c>
-      <c r="O7" s="8" t="inlineStr">
-        <is>
-          <t>(B) FUSHI escuro (Andarilho)(.)/Ryoku (Sukuna)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - boss cataclisma</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Maelra</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>BOSS CATACLISMA</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Companhia da Maré Livre</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Praia</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="11" t="inlineStr">
-        <is>
-          <t>requer VFX</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>(E) Aventureiros Maré (Mar)/Maelra (Cura)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - boss cataclisma</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Veyra</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>BOSS CATACLISMA</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Companhia da Maré Livre</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Praia</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="11" t="inlineStr">
-        <is>
-          <t>requer VFX</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
-        </is>
-      </c>
-      <c r="O9" s="8" t="inlineStr">
-        <is>
-          <t>(E) Aventureiros Maré (Mar)/Veyra (Yumeko)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - ficha avancada</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Nyx</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>FICHA AVANCADA / BOSS</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Companhia da Maré Livre</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Litoral</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>requer VFX</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com mecanicas especiais, imagem/lore e interludio.</t>
-        </is>
-      </c>
-      <c r="O10" s="8" t="inlineStr">
-        <is>
-          <t>(E) Aventureiros Maré (Mar)/Nyx (Cyber Punk Gamer)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - ficha avancada</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Morghast</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>FICHA AVANCADA / BOSS</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Guardiões do Vulcão</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Vulcão</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="11" t="inlineStr">
-        <is>
-          <t>requer VFX</t>
-        </is>
-      </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com mecanicas especiais, imagem/lore e interludio.</t>
-        </is>
-      </c>
-      <c r="O11" s="8" t="inlineStr">
-        <is>
-          <t>(F) Guardiões (Vulcão)/Morghast (Guardião 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - ficha avancada</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Euryaleth</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>FICHA AVANCADA / BOSS</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Guardiões do Vulcão</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Vulcão</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>nao detectado</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com mecanicas especiais, imagem/lore e interludio.</t>
-        </is>
-      </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>(F) Guardiões (Vulcão)/Euryaleth (Guardião 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - ficha avancada</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Vorashk</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>FICHA AVANCADA / BOSS</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Guardiões do Vulcão</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Vulcão</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>nao detectado</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com mecanicas especiais, imagem/lore e interludio.</t>
-        </is>
-      </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>(F) Guardiões (Vulcão)/Vorashk (Guardião 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - ficha avancada</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Aeronyx</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>FICHA AVANCADA / BOSS</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Guardiões do Vulcão</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Vulcão</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="11" t="inlineStr">
-        <is>
-          <t>requer VFX</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com mecanicas especiais, imagem/lore e interludio.</t>
-        </is>
-      </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>(F) Guardiões (Vulcão)/Aeronyx (Guardião 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - ficha avancada</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Thal’Zhyr</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>FICHA AVANCADA / BOSS</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Guardiões do Vulcão</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Oceano</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>nao detectado</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com mecanicas especiais, imagem/lore e interludio.</t>
-        </is>
-      </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>(F) Guardiões (Vulcão)/Thal’Zhyr (Guardião 5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - boss cataclisma</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Astrael</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>BOSS CATACLISMA</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Guardiões do Vulcão</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Nucleo Paradoxial</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="10" t="inlineStr">
-        <is>
-          <t>nao detectado</t>
-        </is>
-      </c>
-      <c r="N16" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
-        </is>
-      </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>(F) Guardiões (Vulcão)/Astrael (Guardião 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - boss cataclisma</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Orian</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>BOSS CATACLISMA</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Vila do Conhecimento Absorvido</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Vila Inicial</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="10" t="inlineStr">
-        <is>
-          <t>nao detectado</t>
-        </is>
-      </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
-        </is>
-      </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>(D) Villa (Planicie) (Protagonistas)/Orian (Marido Cartografo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - boss cataclisma</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Kazuo</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>BOSS CATACLISMA</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Vila do Conhecimento Absorvido</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>Vila Inicial</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="10" t="inlineStr">
-        <is>
-          <t>nao detectado</t>
-        </is>
-      </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
-        </is>
-      </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>(D) Villa (Planicie) (Protagonistas)/Kazuo (Mestre de Renji)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>FOCO - boss cataclisma</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Vhazaryon</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>BOSS CATACLISMA</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Guardiões do Vulcão</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Vulcão Selado</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>falta</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>95</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="L19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="11" t="inlineStr">
-        <is>
-          <t>requer VFX</t>
-        </is>
-      </c>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
-        </is>
-      </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>(F) Guardiões (Vulcão)/Vhazaryon (Dragão FUSHI)</t>
         </is>
       </c>
     </row>
@@ -22695,6 +21998,1140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="51" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bosses, Cataclisma E Fichas Avancadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="19" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Planejamento de entidades com fases, mapas, aparencias, VFX/3D, interludios e controle de estado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Personagem</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Classe ficha</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Faccao</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Historia app</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Lore arquivo</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Eventos</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Fases</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Mapas</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Img</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Dominio/VFX</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>Controle necessario</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>Lore path</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - boss cataclisma</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Yanzik</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>BOSS CATACLISMA</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>FUSHI Escuro</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Viajante</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="11" t="inlineStr">
+        <is>
+          <t>requer VFX</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>(B) FUSHI escuro (Andarilho)(.)/Yanzik (Guts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - boss cataclisma</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Seraph</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>BOSS CATACLISMA</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>FUSHI Escuro</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Andarilho</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>requer VFX</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>(B) FUSHI escuro (Andarilho)(.)/Seraph (Griffith)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - boss cataclisma</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Ryoku</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>BOSS CATACLISMA</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>FUSHI Escuro</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Ruinas</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>107</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11" t="inlineStr">
+        <is>
+          <t>requer VFX</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>(B) FUSHI escuro (Andarilho)(.)/Ryoku (Sukuna)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - boss cataclisma</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Maelra</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>BOSS CATACLISMA</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Companhia da Maré Livre</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Praia</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11" t="inlineStr">
+        <is>
+          <t>requer VFX</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>(E) Aventureiros Maré (Mar)/Maelra (Cura)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - boss cataclisma</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Veyra</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>BOSS CATACLISMA</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Companhia da Maré Livre</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Praia</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>requer VFX</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>(E) Aventureiros Maré (Mar)/Veyra (Yumeko)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - ficha avancada</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Nyx</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>FICHA AVANCADA / BOSS</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Companhia da Maré Livre</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Litoral</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>requer VFX</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com mecanicas especiais, imagem/lore e interludio.</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr">
+        <is>
+          <t>(E) Aventureiros Maré (Mar)/Nyx (Cyber Punk Gamer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - ficha avancada</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Morghast</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>FICHA AVANCADA / BOSS</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Guardiões do Vulcão</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Vulcão</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>requer VFX</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com mecanicas especiais, imagem/lore e interludio.</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>(F) Guardiões (Vulcão)/Morghast (Guardião 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - ficha avancada</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Euryaleth</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>FICHA AVANCADA / BOSS</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Guardiões do Vulcão</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Vulcão</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>nao detectado</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com mecanicas especiais, imagem/lore e interludio.</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>(F) Guardiões (Vulcão)/Euryaleth (Guardião 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - ficha avancada</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Vorashk</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>FICHA AVANCADA / BOSS</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Guardiões do Vulcão</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Vulcão</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>nao detectado</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com mecanicas especiais, imagem/lore e interludio.</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>(F) Guardiões (Vulcão)/Vorashk (Guardião 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - ficha avancada</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Aeronyx</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>FICHA AVANCADA / BOSS</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Guardiões do Vulcão</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Vulcão</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>requer VFX</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com mecanicas especiais, imagem/lore e interludio.</t>
+        </is>
+      </c>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>(F) Guardiões (Vulcão)/Aeronyx (Guardião 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - ficha avancada</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Thal’Zhyr</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>FICHA AVANCADA / BOSS</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Guardiões do Vulcão</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Oceano</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>nao detectado</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com mecanicas especiais, imagem/lore e interludio.</t>
+        </is>
+      </c>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>(F) Guardiões (Vulcão)/Thal’Zhyr (Guardião 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - boss cataclisma</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Astrael</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>BOSS CATACLISMA</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Guardiões do Vulcão</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Nucleo Paradoxial</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>nao detectado</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>(F) Guardiões (Vulcão)/Astrael (Guardião 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - boss cataclisma</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Orian</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>BOSS CATACLISMA</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Vila do Conhecimento Absorvido</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Vila Inicial</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>nao detectado</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>(D) Villa (Planicie) (Protagonistas)/Orian (Marido Cartografo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - boss cataclisma</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Kazuo</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>BOSS CATACLISMA</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Vila do Conhecimento Absorvido</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Vila Inicial</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>nao detectado</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>(D) Villa (Planicie) (Protagonistas)/Kazuo (Mestre de Renji)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - boss cataclisma</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Vhazaryon</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>BOSS CATACLISMA</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Guardiões do Vulcão</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Vulcão Selado</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>requer VFX</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>Ficha avancada com fases, mapas, aparencias, VFX/3D, interludios e estado de fase.</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>(F) Guardiões (Vulcão)/Vhazaryon (Dragão FUSHI)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -23124,7 +23561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23691,7 +24128,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29329,7 +29766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -29484,7 +29921,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Protocolo futuro</t>
+          <t>Divergencias</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -29509,9 +29946,9 @@
           <t>0 pronto</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>DIVIDA</t>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>7 pontos</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -29595,17 +30032,17 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Protagonistas</t>
+          <t>Fontes divergentes</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Corpo real + corpo da Vila + premissa</t>
+          <t>Nome, pasta, app e lore precisam bater</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Completar vinculo e transformar lore em mecanica/mesa.</t>
+          <t>Resolver vermelhos e aceitar aliases amarelos.</t>
         </is>
       </c>
     </row>
@@ -29617,37 +30054,59 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
+          <t>Protagonistas</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Corpo real + corpo da Vila + premissa</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Completar vinculo e transformar lore em mecanica/mesa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
           <t>Mundo/Biomas</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Usar o MUN como fonte de mapa</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Separar por bioma, risco, faccao e conteudo pendente.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Mesa atual</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Baseline confiavel</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Nao mexer no app ate a planilha virar fonte clara.</t>
         </is>
@@ -29712,12 +30171,12 @@
     <hyperlink ref="A12" location="'Faccoes'!A1" display="Faccoes"/>
     <hyperlink ref="C12" location="'Conteudo_Futuro'!A1" display="Tema personagens"/>
     <hyperlink ref="E12" location="'Conteudo_Futuro'!A1" display="Topdown animado"/>
-    <hyperlink ref="G12" location="'Backlog'!A1" display="Protocolo futuro"/>
+    <hyperlink ref="G12" location="'Divergencias'!A1" display="Divergencias"/>
     <hyperlink ref="I12" location="'Core_vs_Pack'!A1" display="Release core"/>
     <hyperlink ref="A13" location="'Faccoes'!A1" display="6 grupos"/>
     <hyperlink ref="C13" location="'Conteudo_Futuro'!A1" display="5 vazios"/>
     <hyperlink ref="E13" location="'Conteudo_Futuro'!A1" display="0 pronto"/>
-    <hyperlink ref="G13" location="'Backlog'!A1" display="DIVIDA"/>
+    <hyperlink ref="G13" location="'Divergencias'!A1" display="7 pontos"/>
     <hyperlink ref="I13" location="'Core_vs_Pack'!A1" display="328.8 MiB"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
+++ b/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
@@ -387,8 +387,8 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="DivergenciasTable" displayName="DivergenciasTable" ref="A4:I11" headerRowCount="1">
-  <autoFilter ref="A4:I11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="DivergenciasTable" displayName="DivergenciasTable" ref="A4:I10" headerRowCount="1">
+  <autoFilter ref="A4:I10"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Tipo"/>
@@ -409,7 +409,7 @@
   <autoFilter ref="A4:F12"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Bloco"/>
-    <tableColumn id="2" name="Destino Alpha.84"/>
+    <tableColumn id="2" name="Destino Alpha.88"/>
     <tableColumn id="3" name="Status"/>
     <tableColumn id="4" name="Criterio"/>
     <tableColumn id="5" name="Observacao"/>
@@ -420,8 +420,8 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="MunAssetsTable" displayName="MunAssetsTable" ref="A4:J127" headerRowCount="1">
-  <autoFilter ref="A4:J127"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="MunAssetsTable" displayName="MunAssetsTable" ref="A4:J129" headerRowCount="1">
+  <autoFilter ref="A4:J129"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Nome"/>
@@ -455,8 +455,8 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="ChecklistTable" displayName="ChecklistTable" ref="A4:F14" headerRowCount="1">
-  <autoFilter ref="A4:F14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="ChecklistTable" displayName="ChecklistTable" ref="A4:F19" headerRowCount="1">
+  <autoFilter ref="A4:F19"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Prioridade"/>
     <tableColumn id="2" name="Mecanica"/>
@@ -470,8 +470,8 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="CampaignCharactersTable" displayName="CampaignCharactersTable" ref="A4:L55" headerRowCount="1">
-  <autoFilter ref="A4:L55"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="CampaignCharactersTable" displayName="CampaignCharactersTable" ref="A4:L59" headerRowCount="1">
+  <autoFilter ref="A4:L59"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Grupo"/>
@@ -491,8 +491,8 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="NpcMechanicsTable" displayName="NpcMechanicsTable" ref="A4:X55" headerRowCount="1">
-  <autoFilter ref="A4:X55"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="NpcMechanicsTable" displayName="NpcMechanicsTable" ref="A4:X59" headerRowCount="1">
+  <autoFilter ref="A4:X59"/>
   <tableColumns count="24">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Categoria"/>
@@ -524,8 +524,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ControleRegrasTable" displayName="ControleRegrasTable" ref="G13:G18" headerRowCount="1">
-  <autoFilter ref="G13:G18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ControleRegrasTable" displayName="ControleRegrasTable" ref="G13:G28" headerRowCount="1">
+  <autoFilter ref="G13:G28"/>
   <tableColumns count="1">
     <tableColumn id="7" name="Regra"/>
   </tableColumns>
@@ -534,8 +534,8 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="ProtagonistasTable" displayName="ProtagonistasTable" ref="A4:O11" headerRowCount="1">
-  <autoFilter ref="A4:O11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="ProtagonistasTable" displayName="ProtagonistasTable" ref="A4:O10" headerRowCount="1">
+  <autoFilter ref="A4:O10"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Personagem app"/>
@@ -604,8 +604,8 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="MundoBiomasTable" displayName="MundoBiomasTable" ref="A4:N12" headerRowCount="1">
-  <autoFilter ref="A4:N12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="MundoBiomasTable" displayName="MundoBiomasTable" ref="A4:N13" headerRowCount="1">
+  <autoFilter ref="A4:N13"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Bioma"/>
@@ -643,8 +643,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="AppBaseChecklistTable" displayName="AppBaseChecklistTable" ref="A4:F13" headerRowCount="1">
-  <autoFilter ref="A4:F13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="AppBaseChecklistTable" displayName="AppBaseChecklistTable" ref="A4:F22" headerRowCount="1">
+  <autoFilter ref="A4:F22"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Area"/>
@@ -672,8 +672,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ProtagonistasControleTable" displayName="ProtagonistasControleTable" ref="A4:L11" headerRowCount="1">
-  <autoFilter ref="A4:L11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ProtagonistasControleTable" displayName="ProtagonistasControleTable" ref="A4:L10" headerRowCount="1">
+  <autoFilter ref="A4:L10"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Personagem app"/>
@@ -693,8 +693,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NpcsMobsTable" displayName="NpcsMobsTable" ref="A4:K49" headerRowCount="1">
-  <autoFilter ref="A4:K49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NpcsMobsTable" displayName="NpcsMobsTable" ref="A4:K53" headerRowCount="1">
+  <autoFilter ref="A4:K53"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Grupo"/>
@@ -736,8 +736,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="BiomasMapasTable" displayName="BiomasMapasTable" ref="A4:K12" headerRowCount="1">
-  <autoFilter ref="A4:K12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="BiomasMapasTable" displayName="BiomasMapasTable" ref="A4:K13" headerRowCount="1">
+  <autoFilter ref="A4:K13"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Bioma"/>
@@ -756,8 +756,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="AudioVfxTable" displayName="AudioVfxTable" ref="A4:F13" headerRowCount="1">
-  <autoFilter ref="A4:F13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="AudioVfxTable" displayName="AudioVfxTable" ref="A4:F15" headerRowCount="1">
+  <autoFilter ref="A4:F15"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Tipo"/>
@@ -1059,7 +1059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1374,6 +1374,74 @@
       <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Audio_VFX</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Antes de explicar ou alterar lore canonica, buscar a fonte primaria em 01_LORE/docs; nao substituir explicacao existente por suposicao.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Livro do Jogador deve conter apenas regra publica de mesa; nao expor lore secreta, XP oculto, reencarnacao, natureza real dos protagonistas ou metaplot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Livro no app e PDFs devem nascer de src/data/rulebook; mudanca de regra nao pode ser digitada separadamente em cada formato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Toda frente nova deve comecar com pergunta guiada para o mestre aprovar: o que existe hoje, o que incomoda, sugestao conservadora, decisao aprovada e teste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Combat V2 e a fonte ativa para CA, Bloqueio, Esquiva, critico, manobras, escala de mobs e simulacao; a correcao canonica de 2026-07-13 tornou Esquiva fixa, mas runtime/Livros aguardam o checkmate da matematica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>O Treino Inicial e administrado pelo EVE. Desativar remove mapa/painel temporario e preserva progresso; reiniciar e uma acao separada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Eventos temporarios coexistem no EVE e nunca podem aceitar substituicao completa da sessao enviada por Jogador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Aceite multiplayer vale pela conexao viva do app: navegar entre Mesa, Fluxo, Livro e Multiplayer nao pode recarregar a pagina nem voltar o Jogador para pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Fechar uma apresentacao visual do EVE e local a janela e nunca apaga o resultado canonico; um novo drawId deve abrir novamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Combat V2 e a fonte ativa para CA, Bloqueio, Esquiva, critico, manobras, escala de mobs e simulacao; FUSHI_COMBAT_V2.md prevalece sobre regra V1 conflitante.</t>
         </is>
       </c>
     </row>
@@ -1433,14 +1501,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FUSHI App Readiness - Alpha.84</t>
+          <t>FUSHI App Readiness - Alpha.88</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fonte de verdade para preservar alpha.83 estavel e planejar conteudo.</t>
+          <t>Fonte unica de verdade para preservar a mesa estavel e planejar conteudo.</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1536,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -1498,11 +1566,11 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4366</v>
+        <v>4422.7</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Alvo alpha.84</t>
+          <t>Alvo alpha.88</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1581,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>3074.1</v>
+        <v>3120.6</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
@@ -1528,7 +1596,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>328.8</v>
+        <v>349.2</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -1543,7 +1611,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
@@ -1558,7 +1626,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
@@ -1797,7 +1865,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>119 interludios automaticos; 119/119 thumbs validas; 0 vazias.</t>
+          <t>121 interludios automaticos; 121/121 thumbs validas; 0 vazias.</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1824,7 +1892,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>24 thumbs sao fornecidas pelo core do app em vez da biblioteca local.</t>
+          <t>0 thumbs sao fornecidas pelo core do app em vez da biblioteca local.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1851,7 +1919,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>4366 MiB no pack; 101 originais pesados cobertos por WebP.</t>
+          <t>4422.7 MiB no pack; 103 originais pesados cobertos por WebP.</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -1898,14 +1966,14 @@
           <t>Personagens, NPCs e habilidades</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>CRITICO PARCIAL</t>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>51 fichas do workspace real; 7 protagonistas; 15 bosses/fichas avancadas; 1 criticas.</t>
+          <t>55 fichas do workspace real; 6 protagonistas; 15 bosses/fichas avancadas; 0 criticas.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1959,7 +2027,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>8 biomas; 68 locais; 56 submapas do MUN.</t>
+          <t>9 biomas; 69 locais; 58 submapas do MUN.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -2067,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2421,49 +2489,6 @@
       <c r="I10" s="8" t="inlineStr">
         <is>
           <t>(D) Villa (Planicie) (Protagonistas)/Maira (Mãe de Sélian)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>APP sem pasta lore</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Ordem do Vazio Sereno</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Personagem existe no app, mas nenhuma pasta/arquivo de lore foi vinculado.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>Criar/vincular pasta em 01_LORE ou marcar conscientemente como somente-app.</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>C:\Users\danie\AppData\Roaming\FUSHI\workspace.json</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2531,7 @@
     <row r="2" ht="19" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Decisao alpha.84: app leve, pack jogavel, source/ultra separado.</t>
+          <t>Decisao alpha.88: app leve, pack jogavel, source/ultra separado.</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2543,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Destino Alpha.84</t>
+          <t>Destino Alpha.88</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -2661,7 +2686,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>101 originais cobertos por WebP.</t>
+          <t>103 originais cobertos por WebP.</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -2816,7 +2841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3151,9 +3176,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3203,9 +3228,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3255,9 +3280,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3307,9 +3332,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J12" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3359,9 +3384,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3411,9 +3436,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3463,9 +3488,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3515,9 +3540,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3567,9 +3592,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3619,9 +3644,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3671,9 +3696,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3723,9 +3748,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3775,9 +3800,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3827,9 +3852,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3879,9 +3904,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3931,9 +3956,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -3983,9 +4008,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -4035,9 +4060,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -4087,9 +4112,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -4139,9 +4164,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -4191,9 +4216,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -4243,9 +4268,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -4295,9 +4320,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J31" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -4347,9 +4372,9 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -4512,17 +4537,17 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>planicie_campo_treino_vila_topdown</t>
+          <t>planicie_m3_s1_cartoteca_porao_topdown</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Campo de Treino da Vila</t>
+          <t>M3-S1 - Cartoteca do Porao</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -4542,12 +4567,12 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>maps/planicie/vila/exterior/campo-treino-vila/campo_treino_vila_topdown_4000.png</t>
+          <t>maps/planicie/vila/interior/armazem-comunitario/submapas/M3-S1_cartoteca_porao_topdown_4000.png</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>maps/planicie/vila/exterior/campo-treino-vila/campo_treino_vila_topdown_thumb_640.jpg</t>
+          <t>maps/planicie/vila/interior/armazem-comunitario/submapas/M3-S1_cartoteca_porao_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -4564,17 +4589,17 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>planicie_vila_conhecimento_absorvido_topdown</t>
+          <t>planicie_campo_treino_vila_topdown</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Vila do Conhecimento Absorvido</t>
+          <t>Campo de Treino da Vila</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -4594,17 +4619,17 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>maps/planicie/vila/exterior/vila-planicie/vila_planicie_topdown_4000.png</t>
+          <t>maps/planicie/vila/exterior/campo-treino-vila/campo_treino_vila_topdown_4000.png</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>maps/planicie/vila/exterior/vila-planicie/vila_planicie_topdown_thumb_640.jpg</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+          <t>maps/planicie/vila/exterior/campo-treino-vila/campo_treino_vila_topdown_thumb_640.jpg</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
@@ -4616,17 +4641,17 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>planicie_bosque_baixo_topdown</t>
+          <t>planicie_vila_conhecimento_absorvido_topdown</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Bosque Baixo</t>
+          <t>Vila do Conhecimento Absorvido</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -4646,12 +4671,12 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>maps/planicie/vila/exterior-grande/bosque-baixo/bosque_baixo_topdown_4000.png</t>
+          <t>maps/planicie/vila/exterior/vila-planicie/vila_planicie_topdown_4000.png</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>maps/planicie/vila/exterior-grande/bosque-baixo/bosque_baixo_topdown_thumb_640.jpg</t>
+          <t>maps/planicie/vila/exterior/vila-planicie/vila_planicie_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
@@ -4668,12 +4693,12 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>planicie_riacho_claro_topdown</t>
+          <t>planicie_bosque_baixo_topdown</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Riacho Claro</t>
+          <t>Bosque Baixo</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -4698,12 +4723,12 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>maps/planicie/vila/exterior-grande/riacho-claro/riacho_claro_topdown_4000.png</t>
+          <t>maps/planicie/vila/exterior-grande/bosque-baixo/bosque_baixo_topdown_4000.png</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>maps/planicie/vila/exterior-grande/riacho-claro/riacho_claro_topdown_thumb_640.jpg</t>
+          <t>maps/planicie/vila/exterior-grande/bosque-baixo/bosque_baixo_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
@@ -4720,17 +4745,17 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>planicie_m5_s1_riacho_claro_nilo_liora</t>
+          <t>planicie_riacho_claro_topdown</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>M5-S1 - Riacho Claro: Nilo e Liora</t>
+          <t>Riacho Claro</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -4750,12 +4775,12 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>maps/planicie/vila/exterior-grande/riacho-claro/submapas/M5-S1_riacho_claro_nilo_liora_topdown_4000.png</t>
+          <t>maps/planicie/vila/exterior-grande/riacho-claro/riacho_claro_topdown_4000.png</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>maps/planicie/vila/exterior-grande/riacho-claro/submapas/M5-S1_riacho_claro_nilo_liora_topdown_thumb_640.jpg</t>
+          <t>maps/planicie/vila/exterior-grande/riacho-claro/riacho_claro_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -4772,22 +4797,22 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>veu_acampamento_veu_exterior_topdown</t>
+          <t>planicie_m5_s1_riacho_claro_nilo_liora</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Acampamento do Veu - Exterior</t>
+          <t>M5-S1 - Riacho Claro: Nilo e Liora</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>vale_cinzento_veu</t>
+          <t>planicie_floresta_inicial</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -4802,12 +4827,12 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/base-faccao/acampamento-veu/acampamento_veu_exterior_topdown_4000.png</t>
+          <t>maps/planicie/vila/exterior-grande/riacho-claro/submapas/M5-S1_riacho_claro_nilo_liora_topdown_4000.png</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/base-faccao/acampamento-veu/acampamento_veu_exterior_topdown_thumb_640.jpg</t>
+          <t>maps/planicie/vila/exterior-grande/riacho-claro/submapas/M5-S1_riacho_claro_nilo_liora_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -4824,22 +4849,22 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>veu_acampamento_veu_base_interior_topdown</t>
+          <t>mundo_dos_sonhos_fragmentado_topdown</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Acampamento do Veu - Interior da Base</t>
+          <t>Mundo dos Sonhos - Subconsciente do Fragmentado</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>interior</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>vale_cinzento_veu</t>
+          <t>mundo_interno_fragmentado</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -4854,17 +4879,17 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/base-faccao/acampamento-veu/acampamento_veu_base_interior_topdown_4000.png</t>
+          <t>maps/mundo-dos-sonhos/fragmentado/mundo_dos_sonhos_fragmentado_topdown_4000.png</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/base-faccao/acampamento-veu/acampamento_veu_base_interior_topdown_thumb_640.jpg</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>nao</t>
+          <t>maps/mundo-dos-sonhos/fragmentado/mundo_dos_sonhos_fragmentado_topdown_thumb_640.jpg</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
@@ -4876,17 +4901,17 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>veu_saida_portao_topdown</t>
+          <t>veu_acampamento_veu_exterior_topdown</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Saida do Portao</t>
+          <t>Acampamento do Veu - Exterior</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -4906,12 +4931,12 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/exterior-grande/saida-portao/saida_portao_topdown_4000.png</t>
+          <t>maps/veu-cinzento/base-faccao/acampamento-veu/acampamento_veu_exterior_topdown_4000.png</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/exterior-grande/saida-portao/saida_portao_topdown_thumb_640.jpg</t>
+          <t>maps/veu-cinzento/base-faccao/acampamento-veu/acampamento_veu_exterior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -4928,17 +4953,17 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>veu_ruina_segura_topdown</t>
+          <t>veu_acampamento_veu_base_interior_topdown</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Ruina Segura</t>
+          <t>Acampamento do Veu - Interior da Base</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -4958,12 +4983,12 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/exterior/ruina-segura/ruina_segura_topdown_4000.png</t>
+          <t>maps/veu-cinzento/base-faccao/acampamento-veu/acampamento_veu_base_interior_topdown_4000.png</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/exterior/ruina-segura/ruina_segura_topdown_thumb_640.jpg</t>
+          <t>maps/veu-cinzento/base-faccao/acampamento-veu/acampamento_veu_base_interior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
@@ -4980,17 +5005,17 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>veu_deposito_camuflado_exterior_topdown</t>
+          <t>veu_saida_portao_topdown</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Deposito Camuflado - Exterior</t>
+          <t>Saida do Portao</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -5010,12 +5035,12 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/recurso/deposito-camuflado/deposito_camuflado_exterior_topdown_4000.png</t>
+          <t>maps/veu-cinzento/exterior-grande/saida-portao/saida_portao_topdown_4000.png</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/recurso/deposito-camuflado/deposito_camuflado_exterior_topdown_thumb_640.jpg</t>
+          <t>maps/veu-cinzento/exterior-grande/saida-portao/saida_portao_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -5032,17 +5057,17 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>veu_deposito_camuflado_interior_topdown</t>
+          <t>veu_ruina_segura_topdown</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Deposito Camuflado - Interior</t>
+          <t>Ruina Segura</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>interior</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -5062,12 +5087,12 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/recurso/deposito-camuflado/interior/deposito_camuflado_interior_topdown_4000.png</t>
+          <t>maps/veu-cinzento/exterior/ruina-segura/ruina_segura_topdown_4000.png</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/recurso/deposito-camuflado/interior/deposito_camuflado_interior_topdown_thumb_640.jpg</t>
+          <t>maps/veu-cinzento/exterior/ruina-segura/ruina_segura_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -5084,12 +5109,12 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>veu_trilha_espioes_topdown</t>
+          <t>veu_deposito_camuflado_exterior_topdown</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Trilha dos Espioes</t>
+          <t>Deposito Camuflado - Exterior</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -5114,12 +5139,12 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/exterior/trilha-espioes/trilha_espioes_topdown_4000.png</t>
+          <t>maps/veu-cinzento/recurso/deposito-camuflado/deposito_camuflado_exterior_topdown_4000.png</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/exterior/trilha-espioes/trilha_espioes_topdown_thumb_640.jpg</t>
+          <t>maps/veu-cinzento/recurso/deposito-camuflado/deposito_camuflado_exterior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -5136,17 +5161,17 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>veu_posto_interceptacao_exterior_topdown</t>
+          <t>veu_deposito_camuflado_interior_topdown</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Posto de Interceptacao - Exterior</t>
+          <t>Deposito Camuflado - Interior</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -5166,12 +5191,12 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/base-faccao/posto-interceptacao/posto_interceptacao_exterior_topdown_4000.png</t>
+          <t>maps/veu-cinzento/recurso/deposito-camuflado/interior/deposito_camuflado_interior_topdown_4000.png</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/base-faccao/posto-interceptacao/posto_interceptacao_exterior_topdown_thumb_640.jpg</t>
+          <t>maps/veu-cinzento/recurso/deposito-camuflado/interior/deposito_camuflado_interior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -5188,17 +5213,17 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>veu_posto_interceptacao_bunker_interior_topdown</t>
+          <t>veu_trilha_espioes_topdown</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Posto de Interceptacao - Interior do Bunker</t>
+          <t>Trilha dos Espioes</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>interior</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -5218,12 +5243,12 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/base-faccao/posto-interceptacao/interior/posto_interceptacao_bunker_interior_topdown_4000.png</t>
+          <t>maps/veu-cinzento/exterior/trilha-espioes/trilha_espioes_topdown_4000.png</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/base-faccao/posto-interceptacao/interior/posto_interceptacao_bunker_interior_topdown_thumb_640.jpg</t>
+          <t>maps/veu-cinzento/exterior/trilha-espioes/trilha_espioes_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -5240,17 +5265,17 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>veu_grande_lago_topdown</t>
+          <t>veu_posto_interceptacao_exterior_topdown</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Grande Lago</t>
+          <t>Posto de Interceptacao - Exterior</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -5270,12 +5295,12 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/exterior-grande/grande-lago/grande_lago_topdown_4000.png</t>
+          <t>maps/veu-cinzento/base-faccao/posto-interceptacao/posto_interceptacao_exterior_topdown_4000.png</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/exterior-grande/grande-lago/grande_lago_topdown_thumb_640.jpg</t>
+          <t>maps/veu-cinzento/base-faccao/posto-interceptacao/posto_interceptacao_exterior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -5292,17 +5317,17 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>veu_torre_observacao_exterior</t>
+          <t>veu_posto_interceptacao_bunker_interior_topdown</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Torre de Observacao - Chegada</t>
+          <t>Posto de Interceptacao - Interior do Bunker</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -5322,12 +5347,12 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/torre-observacao/torre_observacao_exterior_topdown_4000.png</t>
+          <t>maps/veu-cinzento/base-faccao/posto-interceptacao/interior/posto_interceptacao_bunker_interior_topdown_4000.png</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/torre-observacao/torre_observacao_exterior_topdown_thumb_640.jpg</t>
+          <t>maps/veu-cinzento/base-faccao/posto-interceptacao/interior/posto_interceptacao_bunker_interior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -5344,17 +5369,17 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>veu_torre_observacao_topo</t>
+          <t>veu_grande_lago_topdown</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Torre de Observacao - Topo</t>
+          <t>Grande Lago</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -5374,12 +5399,12 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/torre-observacao/torre_observacao_topo_observatorio_4000.png</t>
+          <t>maps/veu-cinzento/exterior-grande/grande-lago/grande_lago_topdown_4000.png</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/torre-observacao/torre_observacao_topo_observatorio_thumb_640.jpg</t>
+          <t>maps/veu-cinzento/exterior-grande/grande-lago/grande_lago_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -5396,22 +5421,22 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>floresta_trilha_enraizada_topdown</t>
+          <t>veu_torre_observacao_exterior</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Trilha Enraizada</t>
+          <t>Torre de Observacao - Chegada</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>floresta_mistica</t>
+          <t>vale_cinzento_veu</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -5426,12 +5451,12 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/exterior-grande/trilha-enraizada/trilha_enraizada_topdown_4000.png</t>
+          <t>maps/veu-cinzento/torre-observacao/torre_observacao_exterior_topdown_4000.png</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/exterior-grande/trilha-enraizada/trilha_enraizada_topdown_thumb_640.jpg</t>
+          <t>maps/veu-cinzento/torre-observacao/torre_observacao_exterior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -5448,22 +5473,22 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>floresta_coracao_verde_topdown</t>
+          <t>veu_torre_observacao_topo</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Coracao Verde</t>
+          <t>Torre de Observacao - Topo</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>floresta_mistica</t>
+          <t>vale_cinzento_veu</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -5478,12 +5503,12 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/exterior-grande/coracao-verde/coracao_verde_topdown_4000.png</t>
+          <t>maps/veu-cinzento/torre-observacao/torre_observacao_topo_observatorio_4000.png</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/exterior-grande/coracao-verde/coracao_verde_topdown_thumb_640.jpg</t>
+          <t>maps/veu-cinzento/torre-observacao/torre_observacao_topo_observatorio_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -5500,17 +5525,17 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>floresta_arvore_fushi_vivo_interior_topdown</t>
+          <t>floresta_trilha_enraizada_topdown</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Arvore de FUSHI Vivo - Interior</t>
+          <t>Trilha Enraizada</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>dungeon</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -5530,12 +5555,12 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/interior/arvore-fushi-vivo/arvore_fushi_vivo_interior_topdown_4000.png</t>
+          <t>maps/floresta-mistica/exterior-grande/trilha-enraizada/trilha_enraizada_topdown_4000.png</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/interior/arvore-fushi-vivo/arvore_fushi_vivo_interior_topdown_thumb_640.jpg</t>
+          <t>maps/floresta-mistica/exterior-grande/trilha-enraizada/trilha_enraizada_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -5552,17 +5577,17 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>floresta_laboratorio_abandonado_exterior_topdown</t>
+          <t>floresta_coracao_verde_topdown</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Laboratorio Abandonado - Exterior</t>
+          <t>Coracao Verde</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -5582,12 +5607,12 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/exterior/laboratorio-abandonado/laboratorio_abandonado_exterior_topdown_4000.png</t>
+          <t>maps/floresta-mistica/exterior-grande/coracao-verde/coracao_verde_topdown_4000.png</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/exterior/laboratorio-abandonado/laboratorio_abandonado_exterior_topdown_thumb_640.jpg</t>
+          <t>maps/floresta-mistica/exterior-grande/coracao-verde/coracao_verde_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -5604,17 +5629,17 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>floresta_laboratorio_abandonado_interior_topdown</t>
+          <t>floresta_arvore_fushi_vivo_interior_topdown</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Laboratorio Abandonado - Interior</t>
+          <t>Arvore de FUSHI Vivo - Interior</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>interior</t>
+          <t>dungeon</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -5634,12 +5659,12 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/interior/laboratorio-abandonado/laboratorio_abandonado_interior_topdown_4000.png</t>
+          <t>maps/floresta-mistica/interior/arvore-fushi-vivo/arvore_fushi_vivo_interior_topdown_4000.png</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/interior/laboratorio-abandonado/laboratorio_abandonado_interior_topdown_thumb_640.jpg</t>
+          <t>maps/floresta-mistica/interior/arvore-fushi-vivo/arvore_fushi_vivo_interior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
@@ -5656,12 +5681,12 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>floresta_clareira_animais_topdown</t>
+          <t>floresta_laboratorio_abandonado_exterior_topdown</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Clareira dos Animais</t>
+          <t>Laboratorio Abandonado - Exterior</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -5686,12 +5711,12 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/exterior/clareira-animais/clareira_animais_topdown_4000.png</t>
+          <t>maps/floresta-mistica/exterior/laboratorio-abandonado/laboratorio_abandonado_exterior_topdown_4000.png</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/exterior/clareira-animais/clareira_animais_topdown_thumb_640.jpg</t>
+          <t>maps/floresta-mistica/exterior/laboratorio-abandonado/laboratorio_abandonado_exterior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -5708,17 +5733,17 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>floresta_lago_espelhado_topdown</t>
+          <t>floresta_laboratorio_abandonado_interior_topdown</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Lago Espelhado</t>
+          <t>Laboratorio Abandonado - Interior</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -5738,12 +5763,12 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/exterior/lago-espelhado/lago_espelhado_topdown_4000.png</t>
+          <t>maps/floresta-mistica/interior/laboratorio-abandonado/laboratorio_abandonado_interior_topdown_4000.png</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/exterior/lago-espelhado/lago_espelhado_topdown_thumb_640.jpg</t>
+          <t>maps/floresta-mistica/interior/laboratorio-abandonado/laboratorio_abandonado_interior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -5760,17 +5785,17 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>floresta_arvore_bebe_topdown</t>
+          <t>floresta_clareira_animais_topdown</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Arvore Bebe</t>
+          <t>Clareira dos Animais</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -5790,12 +5815,12 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/exterior-grande/arvore-bebe/arvore_bebe_topdown_4000.png</t>
+          <t>maps/floresta-mistica/exterior/clareira-animais/clareira_animais_topdown_4000.png</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>maps/floresta-mistica/exterior-grande/arvore-bebe/arvore_bebe_topdown_thumb_640.jpg</t>
+          <t>maps/floresta-mistica/exterior/clareira-animais/clareira_animais_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -5812,22 +5837,22 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>praia_naufragos_topdown</t>
+          <t>floresta_lago_espelhado_topdown</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Praia dos Naufragos</t>
+          <t>Lago Espelhado</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>praia_litoral_oceano</t>
+          <t>floresta_mistica</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -5842,12 +5867,12 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior-grande/praia-naufragos/praia_naufragos_topdown_4000.jpg</t>
+          <t>maps/floresta-mistica/exterior/lago-espelhado/lago_espelhado_topdown_4000.png</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior-grande/praia-naufragos/praia_naufragos_topdown_thumb_640.jpg</t>
+          <t>maps/floresta-mistica/exterior/lago-espelhado/lago_espelhado_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -5864,22 +5889,22 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>praia_enseada_azul_topdown</t>
+          <t>floresta_arvore_bebe_topdown</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Enseada Azul</t>
+          <t>Arvore Bebe</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>praia_litoral_oceano</t>
+          <t>floresta_mistica</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -5894,12 +5919,12 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/enseada-azul/enseada_azul_topdown_4000.jpg</t>
+          <t>maps/floresta-mistica/exterior-grande/arvore-bebe/arvore_bebe_topdown_4000.png</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/enseada-azul/enseada_azul_topdown_thumb_640.jpg</t>
+          <t>maps/floresta-mistica/exterior-grande/arvore-bebe/arvore_bebe_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -5916,17 +5941,17 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>praia_embarque_mare_exterior_topdown</t>
+          <t>praia_naufragos_topdown</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Embarque da Mare Livre - Exterior</t>
+          <t>Praia dos Naufragos</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -5946,12 +5971,12 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/base-faccao/embarque-mare/embarque_mare_exterior_topdown_4000.jpg</t>
+          <t>maps/praia/exterior-grande/praia-naufragos/praia_naufragos_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/base-faccao/embarque-mare/embarque_mare_exterior_topdown_thumb_640.jpg</t>
+          <t>maps/praia/exterior-grande/praia-naufragos/praia_naufragos_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -5968,17 +5993,17 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>praia_navio_mare_interior_topdown</t>
+          <t>praia_enseada_azul_topdown</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Navio da Mare Livre - Interior</t>
+          <t>Enseada Azul</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>interior</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -5998,12 +6023,12 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/base-faccao/embarque-mare/interior/navio_mare_interior_topdown_4000.jpg</t>
+          <t>maps/praia/exterior/enseada-azul/enseada_azul_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/base-faccao/embarque-mare/interior/navio_mare_interior_topdown_thumb_640.jpg</t>
+          <t>maps/praia/exterior/enseada-azul/enseada_azul_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -6020,17 +6045,17 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>praia_recife_cortante_topdown</t>
+          <t>praia_embarque_mare_exterior_topdown</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Recife Cortante</t>
+          <t>Embarque da Mare Livre - Exterior</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
@@ -6050,12 +6075,12 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/recife-cortante/recife_cortante_topdown_4000.jpg</t>
+          <t>maps/praia/base-faccao/embarque-mare/embarque_mare_exterior_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/recife-cortante/recife_cortante_topdown_thumb_640.jpg</t>
+          <t>maps/praia/base-faccao/embarque-mare/embarque_mare_exterior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
@@ -6072,17 +6097,17 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>praia_alto_mar_topdown</t>
+          <t>praia_navio_mare_interior_topdown</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Alto Mar</t>
+          <t>Navio da Mare Livre - Interior</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
@@ -6102,12 +6127,12 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/alto-mar/alto_mar_topdown_4000.jpg</t>
+          <t>maps/praia/base-faccao/embarque-mare/interior/navio_mare_interior_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/alto-mar/alto_mar_topdown_thumb_640.jpg</t>
+          <t>maps/praia/base-faccao/embarque-mare/interior/navio_mare_interior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -6124,17 +6149,17 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>praia_alto_mar_santuario_submerso_topdown</t>
+          <t>praia_recife_cortante_topdown</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Alto Mar - Santuario Submerso</t>
+          <t>Recife Cortante</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>dungeon</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -6154,12 +6179,12 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/alto-mar/submerso/alto_mar_santuario_submerso_topdown_4000.jpg</t>
+          <t>maps/praia/exterior/recife-cortante/recife_cortante_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/alto-mar/submerso/alto_mar_santuario_submerso_topdown_thumb_640.jpg</t>
+          <t>maps/praia/exterior/recife-cortante/recife_cortante_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
@@ -6176,12 +6201,12 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>praia_farol_quebrado_exterior_topdown</t>
+          <t>praia_alto_mar_topdown</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Farol Quebrado - Exterior</t>
+          <t>Alto Mar</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -6206,12 +6231,12 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/farol-quebrado/farol_quebrado_exterior_topdown_4000.jpg</t>
+          <t>maps/praia/exterior/alto-mar/alto_mar_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/farol-quebrado/farol_quebrado_exterior_topdown_thumb_640.jpg</t>
+          <t>maps/praia/exterior/alto-mar/alto_mar_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
@@ -6228,17 +6253,17 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>praia_farol_quebrado_interior_topdown</t>
+          <t>praia_alto_mar_santuario_submerso_topdown</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Farol Quebrado - Interior</t>
+          <t>Alto Mar - Santuario Submerso</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>interior</t>
+          <t>dungeon</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -6258,12 +6283,12 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/farol-quebrado/interior/farol_quebrado_interior_topdown_4000.jpg</t>
+          <t>maps/praia/exterior/alto-mar/submerso/alto_mar_santuario_submerso_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/farol-quebrado/interior/farol_quebrado_interior_topdown_thumb_640.jpg</t>
+          <t>maps/praia/exterior/alto-mar/submerso/alto_mar_santuario_submerso_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -6280,17 +6305,17 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>praia_caverna_mare_topdown</t>
+          <t>praia_farol_quebrado_exterior_topdown</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Caverna da Mare</t>
+          <t>Farol Quebrado - Exterior</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>interior</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -6310,12 +6335,12 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/interior/caverna-mare/caverna_mare_topdown_4000.jpg</t>
+          <t>maps/praia/exterior/farol-quebrado/farol_quebrado_exterior_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/interior/caverna-mare/caverna_mare_topdown_thumb_640.jpg</t>
+          <t>maps/praia/exterior/farol-quebrado/farol_quebrado_exterior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -6332,17 +6357,17 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>praia_costa_ossos_exterior_topdown</t>
+          <t>praia_farol_quebrado_interior_topdown</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Costa dos Ossos</t>
+          <t>Farol Quebrado - Interior</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -6362,12 +6387,12 @@
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/dungeon/costa-ossos/costa_ossos_exterior_topdown_4000.jpg</t>
+          <t>maps/praia/exterior/farol-quebrado/interior/farol_quebrado_interior_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/dungeon/costa-ossos/costa_ossos_exterior_topdown_thumb_640.jpg</t>
+          <t>maps/praia/exterior/farol-quebrado/interior/farol_quebrado_interior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -6384,17 +6409,17 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>praia_caverna_cachoeira_ossos_topdown</t>
+          <t>praia_caverna_mare_topdown</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Costa dos Ossos - Caverna da Cachoeira</t>
+          <t>Caverna da Mare</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>dungeon</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -6414,12 +6439,12 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/dungeon/costa-ossos/interior/caverna_cachoeira_ossos_topdown_4000.jpg</t>
+          <t>maps/praia/interior/caverna-mare/caverna_mare_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/dungeon/costa-ossos/interior/caverna_cachoeira_ossos_topdown_thumb_640.jpg</t>
+          <t>maps/praia/interior/caverna-mare/caverna_mare_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -6436,12 +6461,12 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>praia_estatuas_litoral_topdown</t>
+          <t>praia_costa_ossos_exterior_topdown</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Estatuas do Litoral</t>
+          <t>Costa dos Ossos</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -6466,12 +6491,12 @@
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/estatuas-litoral/estatuas_litoral_topdown_4000.jpg</t>
+          <t>maps/praia/dungeon/costa-ossos/costa_ossos_exterior_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>maps/praia/exterior/estatuas-litoral/estatuas_litoral_topdown_thumb_640.jpg</t>
+          <t>maps/praia/dungeon/costa-ossos/costa_ossos_exterior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
@@ -6488,22 +6513,22 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>montanha_caverna_meditacao_exterior_topdown</t>
+          <t>praia_caverna_cachoeira_ossos_topdown</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Caverna de Meditacao - Chegada</t>
+          <t>Costa dos Ossos - Caverna da Cachoeira</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>dungeon</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>montanhas_vazio_sereno</t>
+          <t>praia_litoral_oceano</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -6518,12 +6543,12 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior-grande/caverna-meditacao/caverna_meditacao_exterior_topdown_4000.jpg</t>
+          <t>maps/praia/dungeon/costa-ossos/interior/caverna_cachoeira_ossos_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior-grande/caverna-meditacao/caverna_meditacao_exterior_topdown_thumb_640.jpg</t>
+          <t>maps/praia/dungeon/costa-ossos/interior/caverna_cachoeira_ossos_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
@@ -6540,22 +6565,22 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>montanha_caverna_meditacao_interior_topdown</t>
+          <t>praia_estatuas_litoral_topdown</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Caverna de Meditacao - Interior</t>
+          <t>Estatuas do Litoral</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>interior</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>montanhas_vazio_sereno</t>
+          <t>praia_litoral_oceano</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -6570,12 +6595,12 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior-grande/caverna-meditacao/interior/caverna_meditacao_interior_topdown_4000.jpg</t>
+          <t>maps/praia/exterior/estatuas-litoral/estatuas_litoral_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior-grande/caverna-meditacao/interior/caverna_meditacao_interior_topdown_thumb_640.jpg</t>
+          <t>maps/praia/exterior/estatuas-litoral/estatuas_litoral_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
@@ -6592,17 +6617,17 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>montanha_templo_vazio_sereno_exterior_topdown</t>
+          <t>montanha_caverna_meditacao_exterior_topdown</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Templo do Vazio Sereno - Exterior</t>
+          <t>Caverna de Meditacao - Chegada</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -6622,12 +6647,12 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/base-faccao/templo-vazio-sereno/templo_vazio_sereno_exterior_topdown_4000.jpg</t>
+          <t>maps/montanha/exterior-grande/caverna-meditacao/caverna_meditacao_exterior_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/base-faccao/templo-vazio-sereno/templo_vazio_sereno_exterior_topdown_thumb_640.jpg</t>
+          <t>maps/montanha/exterior-grande/caverna-meditacao/caverna_meditacao_exterior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
@@ -6644,12 +6669,12 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>montanha_templo_vazio_sereno_interior_topdown</t>
+          <t>montanha_caverna_meditacao_interior_topdown</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Templo do Vazio Sereno - Interior</t>
+          <t>Caverna de Meditacao - Interior</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -6674,12 +6699,12 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/base-faccao/templo-vazio-sereno/interior/templo_vazio_sereno_interior_topdown_4000.jpg</t>
+          <t>maps/montanha/exterior-grande/caverna-meditacao/interior/caverna_meditacao_interior_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/base-faccao/templo-vazio-sereno/interior/templo_vazio_sereno_interior_topdown_thumb_640.jpg</t>
+          <t>maps/montanha/exterior-grande/caverna-meditacao/interior/caverna_meditacao_interior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -6696,17 +6721,17 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>montanha_ponte_suspensa_topdown</t>
+          <t>montanha_templo_vazio_sereno_exterior_topdown</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Ponte Suspensa</t>
+          <t>Templo do Vazio Sereno - Exterior</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
@@ -6726,12 +6751,12 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior/ponte-suspensa/ponte_suspensa_topdown_4000.jpg</t>
+          <t>maps/montanha/base-faccao/templo-vazio-sereno/templo_vazio_sereno_exterior_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior/ponte-suspensa/ponte_suspensa_topdown_thumb_640.jpg</t>
+          <t>maps/montanha/base-faccao/templo-vazio-sereno/templo_vazio_sereno_exterior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
@@ -6748,17 +6773,17 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>montanha_poco_yin_yang_topdown</t>
+          <t>montanha_templo_vazio_sereno_interior_topdown</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Ponte Suspensa - Poco Yin-Yang</t>
+          <t>Templo do Vazio Sereno - Interior</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -6778,12 +6803,12 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior/ponte-suspensa/poco-yin-yang/poco_yin_yang_topdown_4000.jpg</t>
+          <t>maps/montanha/base-faccao/templo-vazio-sereno/interior/templo_vazio_sereno_interior_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior/ponte-suspensa/poco-yin-yang/poco_yin_yang_topdown_thumb_640.jpg</t>
+          <t>maps/montanha/base-faccao/templo-vazio-sereno/interior/templo_vazio_sereno_interior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -6800,17 +6825,17 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>montanha_pico_quatro_ventos_exterior_topdown</t>
+          <t>montanha_ponte_suspensa_topdown</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Pico dos Quatro Ventos - Subida</t>
+          <t>Ponte Suspensa</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
@@ -6830,12 +6855,12 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior-grande/pico-quatro-ventos/pico_quatro_ventos_exterior_topdown_4000.jpg</t>
+          <t>maps/montanha/exterior/ponte-suspensa/ponte_suspensa_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior-grande/pico-quatro-ventos/pico_quatro_ventos_exterior_topdown_thumb_640.jpg</t>
+          <t>maps/montanha/exterior/ponte-suspensa/ponte_suspensa_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
@@ -6852,17 +6877,17 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>montanha_santuario_quatro_ventos_interior_topdown</t>
+          <t>montanha_poco_yin_yang_topdown</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Pico dos Quatro Ventos - Santuario</t>
+          <t>Ponte Suspensa - Poco Yin-Yang</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>interior</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -6882,12 +6907,12 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior-grande/pico-quatro-ventos/interior/santuario_quatro_ventos_interior_topdown_4000.jpg</t>
+          <t>maps/montanha/exterior/ponte-suspensa/poco-yin-yang/poco_yin_yang_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior-grande/pico-quatro-ventos/interior/santuario_quatro_ventos_interior_topdown_thumb_640.jpg</t>
+          <t>maps/montanha/exterior/ponte-suspensa/poco-yin-yang/poco_yin_yang_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
@@ -6904,17 +6929,17 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>montanha_arena_natural_pedra_topdown</t>
+          <t>montanha_pico_quatro_ventos_exterior_topdown</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Arena Natural de Pedra</t>
+          <t>Pico dos Quatro Ventos - Subida</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
@@ -6934,12 +6959,12 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior/arena-natural-pedra/arena_natural_pedra_topdown_4000.jpg</t>
+          <t>maps/montanha/exterior-grande/pico-quatro-ventos/pico_quatro_ventos_exterior_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior/arena-natural-pedra/arena_natural_pedra_topdown_thumb_640.jpg</t>
+          <t>maps/montanha/exterior-grande/pico-quatro-ventos/pico_quatro_ventos_exterior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
@@ -6956,17 +6981,17 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>montanha_saida_montanhas_topdown</t>
+          <t>montanha_santuario_quatro_ventos_interior_topdown</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Saida das Montanhas</t>
+          <t>Pico dos Quatro Ventos - Santuario</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
@@ -6986,12 +7011,12 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior-grande/saida-montanhas/saida_montanhas_topdown_4000.jpg</t>
+          <t>maps/montanha/exterior-grande/pico-quatro-ventos/interior/santuario_quatro_ventos_interior_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>maps/montanha/exterior-grande/saida-montanhas/saida_montanhas_topdown_thumb_640.jpg</t>
+          <t>maps/montanha/exterior-grande/pico-quatro-ventos/interior/santuario_quatro_ventos_interior_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
@@ -7008,22 +7033,22 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>gelo_m22_vale_branco</t>
+          <t>montanha_arena_natural_pedra_topdown</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>M22 - Vale Branco</t>
+          <t>Arena Natural de Pedra</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>regiao_congelada_neve</t>
+          <t>montanhas_vazio_sereno</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -7038,12 +7063,12 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/vale-branco/M22_vale_branco_topdown_4000.png</t>
+          <t>maps/montanha/exterior/arena-natural-pedra/arena_natural_pedra_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/vale-branco/M22_vale_branco_topdown_thumb_640.jpg</t>
+          <t>maps/montanha/exterior/arena-natural-pedra/arena_natural_pedra_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
@@ -7060,22 +7085,22 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>gelo_m23_fortaleza_soterrada</t>
+          <t>montanha_saida_montanhas_topdown</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>M23 - Fortaleza Soterrada</t>
+          <t>Saida das Montanhas</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>dungeon</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>regiao_congelada_neve</t>
+          <t>montanhas_vazio_sereno</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -7090,12 +7115,12 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/fortaleza-soterrada/M23_fortaleza_soterrada_topdown_4000.png</t>
+          <t>maps/montanha/exterior-grande/saida-montanhas/saida_montanhas_topdown_4000.jpg</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/fortaleza-soterrada/M23_fortaleza_soterrada_topdown_thumb_640.jpg</t>
+          <t>maps/montanha/exterior-grande/saida-montanhas/saida_montanhas_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
@@ -7112,17 +7137,17 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>gelo_m24_lago_congelado</t>
+          <t>gelo_m22_vale_branco</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>M24 - Lago Congelado</t>
+          <t>M22 - Vale Branco</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
@@ -7142,12 +7167,12 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/lago-congelado/M24_lago_congelado_topdown_4000.png</t>
+          <t>maps/gelo/base/vale-branco/M22_vale_branco_topdown_4000.png</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/lago-congelado/M24_lago_congelado_topdown_thumb_640.jpg</t>
+          <t>maps/gelo/base/vale-branco/M22_vale_branco_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
@@ -7164,17 +7189,17 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>gelo_m25_grande_avalanche</t>
+          <t>gelo_m23_fortaleza_soterrada</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>M25 - Grande Avalanche</t>
+          <t>M23 - Fortaleza Soterrada</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>dungeon</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -7194,12 +7219,12 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/grande-avalanche/M25_grande_avalanche_topdown_4000.png</t>
+          <t>maps/gelo/base/fortaleza-soterrada/M23_fortaleza_soterrada_topdown_4000.png</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/grande-avalanche/M25_grande_avalanche_topdown_thumb_640.jpg</t>
+          <t>maps/gelo/base/fortaleza-soterrada/M23_fortaleza_soterrada_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
@@ -7216,17 +7241,17 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>gelo_m26_caverna_azul</t>
+          <t>gelo_m24_lago_congelado</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>M26 - Caverna Azul</t>
+          <t>M24 - Lago Congelado</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>dungeon</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
@@ -7246,12 +7271,12 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/caverna-azul/M26_caverna_azul_topdown_4000.png</t>
+          <t>maps/gelo/base/lago-congelado/M24_lago_congelado_topdown_4000.png</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/caverna-azul/M26_caverna_azul_topdown_thumb_640.jpg</t>
+          <t>maps/gelo/base/lago-congelado/M24_lago_congelado_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
@@ -7268,12 +7293,12 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>gelo_m27_bonecos_de_neve</t>
+          <t>gelo_m25_grande_avalanche</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>M27 - Bonecos de Neve</t>
+          <t>M25 - Grande Avalanche</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -7298,12 +7323,12 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/bonecos-de-neve/M27_bonecos_de_neve_topdown_4000.png</t>
+          <t>maps/gelo/base/grande-avalanche/M25_grande_avalanche_topdown_4000.png</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/bonecos-de-neve/M27_bonecos_de_neve_topdown_thumb_640.jpg</t>
+          <t>maps/gelo/base/grande-avalanche/M25_grande_avalanche_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
@@ -7320,12 +7345,12 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>gelo_m28_santuario_sob_gelo</t>
+          <t>gelo_m26_caverna_azul</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>M28 - Santuario Sob o Gelo</t>
+          <t>M26 - Caverna Azul</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -7350,12 +7375,12 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/santuario-sob-gelo/M28_santuario_sob_gelo_topdown_4000.png</t>
+          <t>maps/gelo/base/caverna-azul/M26_caverna_azul_topdown_4000.png</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>maps/gelo/base/santuario-sob-gelo/M28_santuario_sob_gelo_topdown_thumb_640.jpg</t>
+          <t>maps/gelo/base/caverna-azul/M26_caverna_azul_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
@@ -7372,22 +7397,22 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>ruinas_m29_terras_podres</t>
+          <t>gelo_m27_bonecos_de_neve</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>M29 - Terras Podres</t>
+          <t>M27 - Bonecos de Neve</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>ruinas_antigas_ryoku</t>
+          <t>regiao_congelada_neve</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -7402,12 +7427,12 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/terras-podres/M29_terras_podres_topdown_4000.png</t>
+          <t>maps/gelo/base/bonecos-de-neve/M27_bonecos_de_neve_topdown_4000.png</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/terras-podres/M29_terras_podres_topdown_thumb_640.jpg</t>
+          <t>maps/gelo/base/bonecos-de-neve/M27_bonecos_de_neve_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
@@ -7424,22 +7449,22 @@
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>ruinas_m30_s1_portao_torre_abismo</t>
+          <t>gelo_m28_santuario_sob_gelo</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>M30-S1 - Entrada da Torre do Abismo</t>
+          <t>M28 - Santuario Sob o Gelo</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>dungeon</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>ruinas_antigas_ryoku</t>
+          <t>regiao_congelada_neve</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
@@ -7454,12 +7479,12 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/torre-abismo/M30-S1_portao_torre_abismo_topdown_4000.png</t>
+          <t>maps/gelo/base/santuario-sob-gelo/M28_santuario_sob_gelo_topdown_4000.png</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/torre-abismo/M30-S1_portao_torre_abismo_topdown_thumb_640.jpg</t>
+          <t>maps/gelo/base/santuario-sob-gelo/M28_santuario_sob_gelo_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
@@ -7476,17 +7501,17 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>ruinas_m30_torre_abismo</t>
+          <t>ruinas_m29_terras_podres</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>M30-S2 - Camara dos Fragmentos</t>
+          <t>M29 - Terras Podres</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>dungeon</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -7506,12 +7531,12 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/torre-abismo/M30_torre_abismo_topdown_4000.png</t>
+          <t>maps/ruinas/base/terras-podres/M29_terras_podres_topdown_4000.png</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/torre-abismo/M30_torre_abismo_topdown_thumb_640.jpg</t>
+          <t>maps/ruinas/base/terras-podres/M29_terras_podres_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
@@ -7528,17 +7553,17 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>ruinas_m30_s3_corpo_petrificado_ryoku</t>
+          <t>ruinas_m30_s1_portao_torre_abismo</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>M30-S3 - Corpo Petrificado de Ryoku</t>
+          <t>M30-S1 - Entrada da Torre do Abismo</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>interior</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
@@ -7558,12 +7583,12 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/torre-abismo/M30-S3_corpo_petrificado_ryoku_topdown_4000.png</t>
+          <t>maps/ruinas/base/torre-abismo/M30-S1_portao_torre_abismo_topdown_4000.png</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/torre-abismo/M30-S3_corpo_petrificado_ryoku_topdown_thumb_640.jpg</t>
+          <t>maps/ruinas/base/torre-abismo/M30-S1_portao_torre_abismo_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
@@ -7580,17 +7605,17 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>ruinas_m30_s4_torre_despertando</t>
+          <t>ruinas_m30_torre_abismo</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>M30-S4 - Torre do Abismo Despertando</t>
+          <t>M30-S2 - Camara dos Fragmentos</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>dungeon</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -7610,12 +7635,12 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/torre-abismo/M30-S4_torre_abismo_despertando_topdown_4000.png</t>
+          <t>maps/ruinas/base/torre-abismo/M30_torre_abismo_topdown_4000.png</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/torre-abismo/M30-S4_torre_abismo_despertando_topdown_thumb_640.jpg</t>
+          <t>maps/ruinas/base/torre-abismo/M30_torre_abismo_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
@@ -7632,17 +7657,17 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>ruinas_m31_corredor_vozes</t>
+          <t>ruinas_m30_s3_corpo_petrificado_ryoku</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>M31 - Corredor das Vozes</t>
+          <t>M30-S3 - Corpo Petrificado de Ryoku</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>dungeon</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
@@ -7662,12 +7687,12 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/corredor-vozes/M31_corredor_vozes_topdown_4000.png</t>
+          <t>maps/ruinas/base/torre-abismo/M30-S3_corpo_petrificado_ryoku_topdown_4000.png</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/corredor-vozes/M31_corredor_vozes_topdown_thumb_640.jpg</t>
+          <t>maps/ruinas/base/torre-abismo/M30-S3_corpo_petrificado_ryoku_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
@@ -7684,12 +7709,12 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>ruinas_m32_altar_quebrado</t>
+          <t>ruinas_m30_s4_torre_despertando</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>M32 - Altar Quebrado</t>
+          <t>M30-S4 - Torre do Abismo Despertando</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
@@ -7714,12 +7739,12 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/altar-quebrado/M32_altar_quebrado_topdown_4000.png</t>
+          <t>maps/ruinas/base/torre-abismo/M30-S4_torre_abismo_despertando_topdown_4000.png</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/altar-quebrado/M32_altar_quebrado_topdown_thumb_640.jpg</t>
+          <t>maps/ruinas/base/torre-abismo/M30-S4_torre_abismo_despertando_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr">
@@ -7736,17 +7761,17 @@
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>ruinas_m33_s1_entrada_estruturas</t>
+          <t>ruinas_m31_corredor_vozes</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>M33-S1 - Entrada das Estruturas</t>
+          <t>M31 - Corredor das Vozes</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>dungeon</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
@@ -7766,12 +7791,12 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/estruturas-ruinas-abandonadas/M33-S1_entrada_estruturas_topdown_4000.png</t>
+          <t>maps/ruinas/base/corredor-vozes/M31_corredor_vozes_topdown_4000.png</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/estruturas-ruinas-abandonadas/M33-S1_entrada_estruturas_topdown_thumb_640.jpg</t>
+          <t>maps/ruinas/base/corredor-vozes/M31_corredor_vozes_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr">
@@ -7788,12 +7813,12 @@
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>ruinas_m33_s2_parkour_forma_instavel</t>
+          <t>ruinas_m32_altar_quebrado</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>M33-S2 - Parkour da Forma Instavel</t>
+          <t>M32 - Altar Quebrado</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
@@ -7818,12 +7843,12 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/estruturas-ruinas-abandonadas/M33-S2_parkour_forma_instavel_topdown_4000.png</t>
+          <t>maps/ruinas/base/altar-quebrado/M32_altar_quebrado_topdown_4000.png</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/estruturas-ruinas-abandonadas/M33-S2_parkour_forma_instavel_topdown_thumb_640.jpg</t>
+          <t>maps/ruinas/base/altar-quebrado/M32_altar_quebrado_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
@@ -7840,17 +7865,17 @@
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>ruinas_m34_biblioteca_morta</t>
+          <t>ruinas_m33_s1_entrada_estruturas</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>M34 - Biblioteca Morta</t>
+          <t>M33-S1 - Entrada das Estruturas</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>interior</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
@@ -7870,12 +7895,12 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/biblioteca-morta/M34_biblioteca_morta_topdown_4000.png</t>
+          <t>maps/ruinas/base/estruturas-ruinas-abandonadas/M33-S1_entrada_estruturas_topdown_4000.png</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/biblioteca-morta/M34_biblioteca_morta_topdown_thumb_640.jpg</t>
+          <t>maps/ruinas/base/estruturas-ruinas-abandonadas/M33-S1_entrada_estruturas_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
@@ -7892,12 +7917,12 @@
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>ruinas_m35_portao_sem_nome</t>
+          <t>ruinas_m33_s2_parkour_forma_instavel</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>M35 - Portao Sem Nome</t>
+          <t>M33-S2 - Parkour da Forma Instavel</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
@@ -7922,12 +7947,12 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/portao-sem-nome/M35_portao_sem_nome_topdown_4000.png</t>
+          <t>maps/ruinas/base/estruturas-ruinas-abandonadas/M33-S2_parkour_forma_instavel_topdown_4000.png</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/portao-sem-nome/M35_portao_sem_nome_topdown_thumb_640.jpg</t>
+          <t>maps/ruinas/base/estruturas-ruinas-abandonadas/M33-S2_parkour_forma_instavel_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
@@ -7944,22 +7969,22 @@
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m13_entrada</t>
+          <t>ruinas_m34_biblioteca_morta</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>M13 - Entrada do Vulcao</t>
+          <t>M34 - Biblioteca Morta</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>vulcao_terras_cinzentas</t>
+          <t>ruinas_antigas_ryoku</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -7974,12 +7999,12 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/vulcao-entrada/M13_vulcao_entrada_topdown_4000.png</t>
+          <t>maps/ruinas/base/biblioteca-morta/M34_biblioteca_morta_topdown_4000.png</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/vulcao-entrada/M13_vulcao_entrada_topdown_thumb_640.jpg</t>
+          <t>maps/ruinas/base/biblioteca-morta/M34_biblioteca_morta_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
@@ -7996,22 +8021,22 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m14_campo_cinzas</t>
+          <t>ruinas_m35_portao_sem_nome</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>M14 - Campo de Cinzas</t>
+          <t>M35 - Portao Sem Nome</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>livre</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>vulcao_terras_cinzentas</t>
+          <t>ruinas_antigas_ryoku</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -8026,12 +8051,12 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/campo-cinzas/M14_campo_cinzas_topdown_4000.png</t>
+          <t>maps/ruinas/base/portao-sem-nome/M35_portao_sem_nome_topdown_4000.png</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/campo-cinzas/M14_campo_cinzas_topdown_thumb_640.jpg</t>
+          <t>maps/ruinas/base/portao-sem-nome/M35_portao_sem_nome_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr">
@@ -8048,17 +8073,17 @@
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m14_s1_nucleo_rachado</t>
+          <t>vulcao_m13_entrada</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>M14-S1 - Nucleo Paradoxal Rachado</t>
+          <t>M13 - Entrada do Vulcao</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
@@ -8078,12 +8103,12 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/campo-cinzas/M14-S1_nucleo_rachado_topdown_4000.png</t>
+          <t>maps/vulcao/base/vulcao-entrada/M13_vulcao_entrada_topdown_4000.png</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/campo-cinzas/M14-S1_nucleo_rachado_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/vulcao-entrada/M13_vulcao_entrada_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
@@ -8100,17 +8125,17 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m14_s2_nucleo_desperto</t>
+          <t>vulcao_m14_campo_cinzas</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>M14-S2 - Nucleo Paradoxal Desperto</t>
+          <t>M14 - Campo de Cinzas</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -8130,12 +8155,12 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/campo-cinzas/M14-S2_nucleo_desperto_topdown_4000.png</t>
+          <t>maps/vulcao/base/campo-cinzas/M14_campo_cinzas_topdown_4000.png</t>
         </is>
       </c>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/campo-cinzas/M14-S2_nucleo_desperto_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/campo-cinzas/M14_campo_cinzas_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr">
@@ -8152,12 +8177,12 @@
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m15_rio_escuridao</t>
+          <t>vulcao_m14_s1_nucleo_rachado</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>M15 - Rio da Escuridao</t>
+          <t>M14-S1 - Nucleo Paradoxal Rachado</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
@@ -8182,12 +8207,12 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/rio-da-escuridao/M15_rio_da_escuridao_topdown_4000.png</t>
+          <t>maps/vulcao/base/campo-cinzas/M14-S1_nucleo_rachado_topdown_4000.png</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/rio-da-escuridao/M15_rio_da_escuridao_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/campo-cinzas/M14-S1_nucleo_rachado_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I106" s="10" t="inlineStr">
@@ -8204,12 +8229,12 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m15_s1_corrida_abismo</t>
+          <t>vulcao_m14_s2_nucleo_desperto</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>M15-S1 - Corrida do Abismo</t>
+          <t>M14-S2 - Nucleo Paradoxal Desperto</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
@@ -8234,12 +8259,12 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/rio-da-escuridao/M15-S1_corrida_abismo_topdown_4000.png</t>
+          <t>maps/vulcao/base/campo-cinzas/M14-S2_nucleo_desperto_topdown_4000.png</t>
         </is>
       </c>
       <c r="H107" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/rio-da-escuridao/M15-S1_corrida_abismo_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/campo-cinzas/M14-S2_nucleo_desperto_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I107" s="10" t="inlineStr">
@@ -8256,12 +8281,12 @@
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m15_s2_nucleo_sombras</t>
+          <t>vulcao_m15_rio_escuridao</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>M15-S2 - Nucleo das Sombras</t>
+          <t>M15 - Rio da Escuridao</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
@@ -8286,12 +8311,12 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/rio-da-escuridao/M15-S2_nucleo_sombras_topdown_4000.png</t>
+          <t>maps/vulcao/base/rio-da-escuridao/M15_rio_da_escuridao_topdown_4000.png</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/rio-da-escuridao/M15-S2_nucleo_sombras_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/rio-da-escuridao/M15_rio_da_escuridao_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I108" s="10" t="inlineStr">
@@ -8308,12 +8333,12 @@
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m15_s3_takedown_mar_infinito</t>
+          <t>vulcao_m15_s1_corrida_abismo</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>M15-S3 - Takedown: Mar Infinito</t>
+          <t>M15-S1 - Corrida do Abismo</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
@@ -8338,12 +8363,12 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/rio-da-escuridao/M15-S3_takedown_mar_infinito_topdown_4000.png</t>
+          <t>maps/vulcao/base/rio-da-escuridao/M15-S1_corrida_abismo_topdown_4000.png</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/rio-da-escuridao/M15-S3_takedown_mar_infinito_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/rio-da-escuridao/M15-S1_corrida_abismo_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr">
@@ -8360,12 +8385,12 @@
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m16_s1_sala_estatuas_xadrez</t>
+          <t>vulcao_m15_s2_nucleo_sombras</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>M16-S1 - Sala das Estatuas e Tabuleiro</t>
+          <t>M15-S2 - Nucleo das Sombras</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
@@ -8390,12 +8415,12 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/vulcao-abandonado/M16-S1_sala_estatuas_xadrez_topdown_4000.png</t>
+          <t>maps/vulcao/base/rio-da-escuridao/M15-S2_nucleo_sombras_topdown_4000.png</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/vulcao-abandonado/M16-S1_sala_estatuas_xadrez_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/rio-da-escuridao/M15-S2_nucleo_sombras_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I110" s="10" t="inlineStr">
@@ -8412,12 +8437,12 @@
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m16_s2_olhar_estagnacao</t>
+          <t>vulcao_m15_s3_takedown_mar_infinito</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>M16-S2 - Olhar da Estagnacao</t>
+          <t>M15-S3 - Takedown: Mar Infinito</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
@@ -8442,12 +8467,12 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/vulcao-abandonado/M16-S2_olhar_estagnacao_topdown_4000.png</t>
+          <t>maps/vulcao/base/rio-da-escuridao/M15-S3_takedown_mar_infinito_topdown_4000.png</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/vulcao-abandonado/M16-S2_olhar_estagnacao_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/rio-da-escuridao/M15-S3_takedown_mar_infinito_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr">
@@ -8464,12 +8489,12 @@
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m16_s3_escadaria_espiral_aberta</t>
+          <t>vulcao_m16_s1_sala_estatuas_xadrez</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>M16-S3 - Escadaria Espiral Aberta</t>
+          <t>M16-S1 - Sala das Estatuas e Tabuleiro</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
@@ -8494,12 +8519,12 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/vulcao-abandonado/M16-S3_escadaria_espiral_aberta_topdown_4000.png</t>
+          <t>maps/vulcao/base/vulcao-abandonado/M16-S1_sala_estatuas_xadrez_topdown_4000.png</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/vulcao-abandonado/M16-S3_escadaria_espiral_aberta_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/vulcao-abandonado/M16-S1_sala_estatuas_xadrez_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr">
@@ -8516,17 +8541,17 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m17_labirinto_quente_vorashk</t>
+          <t>vulcao_m16_s2_olhar_estagnacao</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>M17 - Labirinto Quente / Vorashk</t>
+          <t>M16-S2 - Olhar da Estagnacao</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>dungeon</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
@@ -8546,12 +8571,12 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/labirinto-quente/M17_labirinto_quente_topdown_4000.png</t>
+          <t>maps/vulcao/base/vulcao-abandonado/M16-S2_olhar_estagnacao_topdown_4000.png</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/labirinto-quente/M17_labirinto_quente_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/vulcao-abandonado/M16-S2_olhar_estagnacao_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
@@ -8568,12 +8593,12 @@
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m17_s1_arena_vorashk_sem_muros</t>
+          <t>vulcao_m16_s3_escadaria_espiral_aberta</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>M17-S1 - Arena de Vorashk sem Muros</t>
+          <t>M16-S3 - Escadaria Espiral Aberta</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
@@ -8598,12 +8623,12 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/labirinto-quente/M17-S1_arena_vorashk_sem_muros_topdown_4000.png</t>
+          <t>maps/vulcao/base/vulcao-abandonado/M16-S3_escadaria_espiral_aberta_topdown_4000.png</t>
         </is>
       </c>
       <c r="H114" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/labirinto-quente/M17-S1_arena_vorashk_sem_muros_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/vulcao-abandonado/M16-S3_escadaria_espiral_aberta_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I114" s="10" t="inlineStr">
@@ -8620,17 +8645,17 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m18_boca_inferno_aeronyx</t>
+          <t>vulcao_m17_labirinto_quente_vorashk</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>M18-S2 - Boca do Inferno / Arena de Aeronyx</t>
+          <t>M17 - Labirinto Quente / Vorashk</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>dungeon</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
@@ -8650,12 +8675,12 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/boca-inferno/M18_boca_inferno_topdown_4000.png</t>
+          <t>maps/vulcao/base/labirinto-quente/M17_labirinto_quente_topdown_4000.png</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/boca-inferno/M18_boca_inferno_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/labirinto-quente/M17_labirinto_quente_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr">
@@ -8672,12 +8697,12 @@
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m18_s1_escadaria_erupcao</t>
+          <t>vulcao_m17_s1_arena_vorashk_sem_muros</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>M18-S1 - Subida da Boca do Inferno</t>
+          <t>M17-S1 - Arena de Vorashk sem Muros</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
@@ -8702,12 +8727,12 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/escadaria-erupcao/M18-S1_escadaria_vulcao_erupcao_topdown_4000.png</t>
+          <t>maps/vulcao/base/labirinto-quente/M17-S1_arena_vorashk_sem_muros_topdown_4000.png</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/escadaria-erupcao/M18-S1_escadaria_vulcao_erupcao_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/labirinto-quente/M17-S1_arena_vorashk_sem_muros_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr">
@@ -8724,12 +8749,12 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m18_s3_chuva_obsidiana</t>
+          <t>vulcao_m18_boca_inferno_aeronyx</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>M18-S3 - Chuva e Obsidiana</t>
+          <t>M18-S2 - Boca do Inferno / Arena de Aeronyx</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
@@ -8754,12 +8779,12 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/boca-inferno/M18-S3_chuva_obsidiana_topdown_4000.png</t>
+          <t>maps/vulcao/base/boca-inferno/M18_boca_inferno_topdown_4000.png</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/boca-inferno/M18-S3_chuva_obsidiana_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/boca-inferno/M18_boca_inferno_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr">
@@ -8776,12 +8801,12 @@
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m19_mar_inquieto_thalzhyr</t>
+          <t>vulcao_m18_s1_escadaria_erupcao</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>M19-S1 - Costa Tempestuosa / Preparacao do Navio</t>
+          <t>M18-S1 - Subida da Boca do Inferno</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
@@ -8806,12 +8831,12 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/mar-inquieto/M19_mar_inquieto_topdown_4000.png</t>
+          <t>maps/vulcao/base/escadaria-erupcao/M18-S1_escadaria_vulcao_erupcao_topdown_4000.png</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/mar-inquieto/M19_mar_inquieto_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/escadaria-erupcao/M18-S1_escadaria_vulcao_erupcao_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
@@ -8828,12 +8853,12 @@
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m19_s2_alto_mar_tempestade</t>
+          <t>vulcao_m18_s3_chuva_obsidiana</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>M19-S2 - Alto Mar / Tempestade</t>
+          <t>M18-S3 - Chuva e Obsidiana</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
@@ -8858,12 +8883,12 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/mar-inquieto/M19-S2_alto_mar_tempestade_topdown_4000.png</t>
+          <t>maps/vulcao/base/boca-inferno/M18-S3_chuva_obsidiana_topdown_4000.png</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/mar-inquieto/M19-S2_alto_mar_tempestade_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/boca-inferno/M18-S3_chuva_obsidiana_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -8880,12 +8905,12 @@
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m19_s3_hidra_thalzhyr</t>
+          <t>vulcao_m19_mar_inquieto_thalzhyr</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>M19-S3 - Hidra no Mar Aberto / Thal'Zhyr</t>
+          <t>M19-S1 - Costa Tempestuosa / Preparacao do Navio</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
@@ -8910,12 +8935,12 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/mar-inquieto/M19-S3_hidra_thalzhyr_topdown_4000.png</t>
+          <t>maps/vulcao/base/mar-inquieto/M19_mar_inquieto_topdown_4000.png</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/mar-inquieto/M19-S3_hidra_thalzhyr_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/mar-inquieto/M19_mar_inquieto_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -8932,12 +8957,12 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m19_s4_mar_colapsando_costa</t>
+          <t>vulcao_m19_s2_alto_mar_tempestade</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>M19-S4 - Mar Colapsando ate a Costa</t>
+          <t>M19-S2 - Alto Mar / Tempestade</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
@@ -8962,12 +8987,12 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/mar-inquieto/M19-S4_mar_colapsando_costa_topdown_4000.png</t>
+          <t>maps/vulcao/base/mar-inquieto/M19-S2_alto_mar_tempestade_topdown_4000.png</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/mar-inquieto/M19-S4_mar_colapsando_costa_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/mar-inquieto/M19-S2_alto_mar_tempestade_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -8984,12 +9009,12 @@
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m20_transcendente_astrael</t>
+          <t>vulcao_m19_s3_hidra_thalzhyr</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>M20 - Transcendente / Astrael</t>
+          <t>M19-S3 - Hidra no Mar Aberto / Thal'Zhyr</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
@@ -9014,12 +9039,12 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/transcendente/M20_transcendente_topdown_4000.png</t>
+          <t>maps/vulcao/base/mar-inquieto/M19-S3_hidra_thalzhyr_topdown_4000.png</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/transcendente/M20_transcendente_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/mar-inquieto/M19-S3_hidra_thalzhyr_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
@@ -9036,12 +9061,12 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m20_s1_observatorio_selo</t>
+          <t>vulcao_m19_s4_mar_colapsando_costa</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>M20-S1 - Observatorio do Selo</t>
+          <t>M19-S4 - Mar Colapsando ate a Costa</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
@@ -9066,12 +9091,12 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/transcendente/M20-S1_observatorio_selo_topdown_4000.png</t>
+          <t>maps/vulcao/base/mar-inquieto/M19-S4_mar_colapsando_costa_topdown_4000.png</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/transcendente/M20-S1_observatorio_selo_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/mar-inquieto/M19-S4_mar_colapsando_costa_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -9088,12 +9113,12 @@
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m20_s2_seis_orbitas</t>
+          <t>vulcao_m20_transcendente_astrael</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>M20-S2 - Seis Orbitas do Vulcao</t>
+          <t>M20 - Transcendente / Astrael</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
@@ -9118,12 +9143,12 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/transcendente/M20-S2_seis_orbitas_topdown_4000.png</t>
+          <t>maps/vulcao/base/transcendente/M20_transcendente_topdown_4000.png</t>
         </is>
       </c>
       <c r="H124" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/transcendente/M20-S2_seis_orbitas_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/transcendente/M20_transcendente_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -9140,12 +9165,12 @@
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m20_s3_ciclo_vorpal</t>
+          <t>vulcao_m20_s1_observatorio_selo</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>M20-S3 - Ciclo Vorpal</t>
+          <t>M20-S1 - Observatorio do Selo</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
@@ -9170,12 +9195,12 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/transcendente/M20-S3_ciclo_vorpal_topdown_4000.png</t>
+          <t>maps/vulcao/base/transcendente/M20-S1_observatorio_selo_topdown_4000.png</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/transcendente/M20-S3_ciclo_vorpal_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/transcendente/M20-S1_observatorio_selo_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
@@ -9192,12 +9217,12 @@
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>vulcao_m20_s4_colapso_selo</t>
+          <t>vulcao_m20_s2_seis_orbitas</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>M20-S4 - Colapso do Ultimo Selo</t>
+          <t>M20-S2 - Seis Orbitas do Vulcao</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
@@ -9222,12 +9247,12 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/transcendente/M20-S4_colapso_selo_topdown_4000.png</t>
+          <t>maps/vulcao/base/transcendente/M20-S2_seis_orbitas_topdown_4000.png</t>
         </is>
       </c>
       <c r="H126" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/transcendente/M20-S4_colapso_selo_topdown_thumb_640.jpg</t>
+          <t>maps/vulcao/base/transcendente/M20-S2_seis_orbitas_topdown_thumb_640.jpg</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr">
@@ -9244,50 +9269,154 @@
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
+          <t>vulcao_m20_s3_ciclo_vorpal</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>M20-S3 - Ciclo Vorpal</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>vulcao_terras_cinzentas</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>OK tecnico</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>maps/vulcao/base/transcendente/M20-S3_ciclo_vorpal_topdown_4000.png</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="inlineStr">
+        <is>
+          <t>maps/vulcao/base/transcendente/M20-S3_ciclo_vorpal_topdown_thumb_640.jpg</t>
+        </is>
+      </c>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>vulcao_m20_s4_colapso_selo</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>M20-S4 - Colapso do Ultimo Selo</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t>vulcao_terras_cinzentas</t>
+        </is>
+      </c>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>OK tecnico</t>
+        </is>
+      </c>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t>maps/vulcao/base/transcendente/M20-S4_colapso_selo_topdown_4000.png</t>
+        </is>
+      </c>
+      <c r="H128" s="8" t="inlineStr">
+        <is>
+          <t>maps/vulcao/base/transcendente/M20-S4_colapso_selo_topdown_thumb_640.jpg</t>
+        </is>
+      </c>
+      <c r="I128" s="10" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="J128" s="7" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
           <t>vulcao_m21_deus_dragao</t>
         </is>
       </c>
-      <c r="B127" s="8" t="inlineStr">
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>M21 - Deus Dragao</t>
         </is>
       </c>
-      <c r="C127" s="8" t="inlineStr">
+      <c r="C129" s="8" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="D127" s="8" t="inlineStr">
+      <c r="D129" s="8" t="inlineStr">
         <is>
           <t>vulcao_terras_cinzentas</t>
         </is>
       </c>
-      <c r="E127" s="8" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="F127" s="7" t="inlineStr">
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
         <is>
           <t>OK tecnico</t>
         </is>
       </c>
-      <c r="G127" s="8" t="inlineStr">
+      <c r="G129" s="8" t="inlineStr">
         <is>
           <t>maps/vulcao/base/deus-dragao/M21_deus_dragao_topdown_4000.png</t>
         </is>
       </c>
-      <c r="H127" s="8" t="inlineStr">
+      <c r="H129" s="8" t="inlineStr">
         <is>
           <t>maps/vulcao/base/deus-dragao/M21_deus_dragao_topdown_thumb_640.jpg</t>
         </is>
       </c>
-      <c r="I127" s="10" t="inlineStr">
+      <c r="I129" s="10" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J127" s="7" t="inlineStr">
+      <c r="J129" s="7" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
@@ -11609,19 +11738,19 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/terras-podres/M29_terras_podres_topdown_4000.png</t>
+          <t>maps/planicie/vila/interior/armazem-comunitario/submapas/M3-S1_cartoteca_porao_topdown_4000.png</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>_optimized/maps/ruinas/base/terras-podres/M29_terras_podres_topdown_4000.webp</t>
+          <t>_optimized/maps/planicie/vila/interior/armazem-comunitario/submapas/M3-S1_cartoteca_porao_topdown_4000.webp</t>
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
@@ -11629,7 +11758,7 @@
         </is>
       </c>
       <c r="F77" s="8" t="n">
-        <v>28.6</v>
+        <v>29.9</v>
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
@@ -11640,7 +11769,7 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/estruturas-ruinas-abandonadas/M33-S1_entrada_estruturas_topdown_4000.png</t>
+          <t>maps/ruinas/base/terras-podres/M29_terras_podres_topdown_4000.png</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
@@ -11648,11 +11777,11 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>_optimized/maps/ruinas/base/estruturas-ruinas-abandonadas/M33-S1_entrada_estruturas_topdown_4000.webp</t>
+          <t>_optimized/maps/ruinas/base/terras-podres/M29_terras_podres_topdown_4000.webp</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
@@ -11660,7 +11789,7 @@
         </is>
       </c>
       <c r="F78" s="8" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
@@ -11671,15 +11800,15 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/corredor-vozes/M31_corredor_vozes_topdown_4000.png</t>
+          <t>maps/ruinas/base/estruturas-ruinas-abandonadas/M33-S1_entrada_estruturas_topdown_4000.png</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>_optimized/maps/ruinas/base/corredor-vozes/M31_corredor_vozes_topdown_4000.webp</t>
+          <t>_optimized/maps/ruinas/base/estruturas-ruinas-abandonadas/M33-S1_entrada_estruturas_topdown_4000.webp</t>
         </is>
       </c>
       <c r="D79" s="8" t="n">
@@ -11691,7 +11820,7 @@
         </is>
       </c>
       <c r="F79" s="8" t="n">
-        <v>28.3</v>
+        <v>28.7</v>
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
@@ -11702,15 +11831,15 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/base-faccao/posto-interceptacao/interior/posto_interceptacao_bunker_interior_topdown_4000.png</t>
+          <t>maps/ruinas/base/corredor-vozes/M31_corredor_vozes_topdown_4000.png</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>_optimized/maps/veu-cinzento/base-faccao/posto-interceptacao/interior/posto_interceptacao_bunker_interior_topdown_4000.webp</t>
+          <t>_optimized/maps/ruinas/base/corredor-vozes/M31_corredor_vozes_topdown_4000.webp</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
@@ -11722,7 +11851,7 @@
         </is>
       </c>
       <c r="F80" s="8" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
@@ -11733,7 +11862,7 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>maps/vulcao/base/rio-da-escuridao/M15_rio_da_escuridao_topdown_4000.png</t>
+          <t>maps/veu-cinzento/base-faccao/posto-interceptacao/interior/posto_interceptacao_bunker_interior_topdown_4000.png</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
@@ -11741,7 +11870,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>_optimized/maps/vulcao/base/rio-da-escuridao/M15_rio_da_escuridao_topdown_4000.webp</t>
+          <t>_optimized/maps/veu-cinzento/base-faccao/posto-interceptacao/interior/posto_interceptacao_bunker_interior_topdown_4000.webp</t>
         </is>
       </c>
       <c r="D81" s="8" t="n">
@@ -11753,7 +11882,7 @@
         </is>
       </c>
       <c r="F81" s="8" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
@@ -11764,19 +11893,19 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/torre-observacao/torre_observacao_topo_observatorio_4000.png</t>
+          <t>maps/vulcao/base/rio-da-escuridao/M15_rio_da_escuridao_topdown_4000.png</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>29.7</v>
+        <v>29.9</v>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>_optimized/maps/veu-cinzento/torre-observacao/torre_observacao_topo_observatorio_4000.webp</t>
+          <t>_optimized/maps/vulcao/base/rio-da-escuridao/M15_rio_da_escuridao_topdown_4000.webp</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
@@ -11784,7 +11913,7 @@
         </is>
       </c>
       <c r="F82" s="8" t="n">
-        <v>28.1</v>
+        <v>28.3</v>
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
@@ -11795,15 +11924,15 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>maps/veu-cinzento/recurso/deposito-camuflado/interior/deposito_camuflado_interior_topdown_4000.png</t>
+          <t>maps/veu-cinzento/torre-observacao/torre_observacao_topo_observatorio_4000.png</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>28.7</v>
+        <v>29.7</v>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>_optimized/maps/veu-cinzento/recurso/deposito-camuflado/interior/deposito_camuflado_interior_topdown_4000.webp</t>
+          <t>_optimized/maps/veu-cinzento/torre-observacao/torre_observacao_topo_observatorio_4000.webp</t>
         </is>
       </c>
       <c r="D83" s="8" t="n">
@@ -11815,7 +11944,7 @@
         </is>
       </c>
       <c r="F83" s="8" t="n">
-        <v>27.1</v>
+        <v>28.1</v>
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
@@ -11826,19 +11955,19 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>maps/ruinas/base/torre-abismo/M30_torre_abismo_topdown_4000.png</t>
+          <t>maps/veu-cinzento/recurso/deposito-camuflado/interior/deposito_camuflado_interior_topdown_4000.png</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>_optimized/maps/ruinas/base/torre-abismo/M30_torre_abismo_topdown_4000.webp</t>
+          <t>_optimized/maps/veu-cinzento/recurso/deposito-camuflado/interior/deposito_camuflado_interior_topdown_4000.webp</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
@@ -11846,7 +11975,7 @@
         </is>
       </c>
       <c r="F84" s="8" t="n">
-        <v>26.2</v>
+        <v>27.1</v>
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
@@ -11872,7 +12001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11893,7 +12022,7 @@
     <row r="2" ht="19" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mecanicas que devem continuar 100% antes de alpha.84 virar base.</t>
+          <t>Gate obrigatorio da alpha.88 e de qualquer build futura que toque multiplayer, ficha, combate ou eventos.</t>
         </is>
       </c>
     </row>
@@ -11937,27 +12066,27 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Regua Mestre -&gt; Jogador</t>
+          <t>Reentrada da sessao</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Mestre mede, arrasta rapido e solta.</t>
+          <t>Depois do aceite, sair para Fluxo/Livro/Multiplayer e voltar; repetir com um socket novo da mesma instancia.</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Jogador ve linha/label sem flicker e final correto.</t>
+          <t>Nao pede novo aceite e estado, dados, ficha e eventos continuam sincronizados; fechar o app ou expulsar revoga a sessao.</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Teste fisico</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>Pendente pro proximo ciclo</t>
+          <t>Smoke multiplayer + release real</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>OK automatizado alpha.88; teste fisico recomendado</t>
         </is>
       </c>
     </row>
@@ -11969,27 +12098,27 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Regua Jogador -&gt; Mestre</t>
+          <t>EVE publico</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Jogador mede, arrasta rapido e solta.</t>
+          <t>Apos a reentrada, Mestre transmite o sorteio de raridade e o jogador dispensa a apresentacao.</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Mestre ve linha/label sem duplicar nem piscar.</t>
+          <t>Todos os jogadores veem a animacao atual, sem dados secretos e sem repetir ultimo roll/backlog ao trocar de cena.</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Teste fisico</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>Pendente pro proximo ciclo</t>
+          <t>Smoke multiplayer + release real</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>OK automatizado alpha.88</t>
         </is>
       </c>
     </row>
@@ -12001,27 +12130,27 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Dados com fila/cooldown</t>
+          <t>Regua Mestre -&gt; Jogador</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Rolar rapido dos dois lados.</t>
+          <t>Mestre mede, arrasta rapido e solta.</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Sem duplicar por retry/lag; ACK idempotente.</t>
+          <t>Jogador ve linha/label sem flicker e final correto.</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Ja responsivo no teste</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>OK observado</t>
+          <t>Teste fisico</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Pendente pro proximo ciclo</t>
         </is>
       </c>
     </row>
@@ -12033,17 +12162,17 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Ficha remota</t>
+          <t>Regua Jogador -&gt; Mestre</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Mestre altera vida/fushi e jogador observa.</t>
+          <t>Jogador mede, arrasta rapido e solta.</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Imagem/ficha nao some e estado persiste.</t>
+          <t>Mestre ve linha/label sem duplicar nem piscar.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -12053,7 +12182,7 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Revalidar</t>
+          <t>Pendente pro proximo ciclo</t>
         </is>
       </c>
     </row>
@@ -12065,185 +12194,345 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
+          <t>Dados com fila/cooldown</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Rolar rapido dos dois lados.</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Sem duplicar por retry/lag; ACK idempotente.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Ja responsivo no teste</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>OK observado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Ficha remota</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Mestre atribui skill/build e altera vida; jogador altera campos permitidos depois da reentrada.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Skills, builds e vida sincronizam nos dois sentidos sem estado antigo apagar campos canonicos do Mestre.</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Smoke multiplayer + release real</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>OK automatizado alpha.88; teste fisico recomendado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Resolver de combate</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Ficha prepara ataque; Dados de Combate escolhe forma e alvo; aguardar dado; confirmar defesa, dano e resultado.</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Nada altera a ficha antes da confirmacao final; cancelar nao gasta recurso; distancia usa snapshot da rolagem.</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Combat runtime + UI + multiplayer</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>OK automatizado alpha.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Recibo privado de combate</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Atacar J2 com J1 e observar Mestre, J1, J2 e um terceiro jogador.</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Mestre ve calculo completo; envolvidos veem somente o proprio recurso; terceiro nao recebe recibo privado.</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Smoke multiplayer</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>OK automatizado alpha.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Queda dos protagonistas</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Levar J1-J5 a 0 Vida; marcar tres sucessos e repetir com tres falhas.</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Caveira publica pisca; tres sucessos recuperam 1 Vida; tres falhas deixam token cinza; NPC nao revela o painel.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Combat flow UI</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>OK automatizado alpha.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
           <t>Interludio MUN</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Abrir map com interludio e pular/voltar.</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Sem tela branca/preta tecnica; thumb coerente.</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Smoke + teste visual</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>OK tecnico</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Preparar MAP</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Mestre prepara mapa e depois ativa.</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Mestre entra no preparo; jogador fica no ativo ate ativar.</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Smoke release deep</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>OK automatizado</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Liberar Base/MUN</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Liberar Base e MUN para jogador.</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Ambos aparecem da mesma forma para players.</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Smoke + teste fisico</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>Revalidar</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>CAM GM 2D/3D</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Mover camera segurando WASD/scroll.</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Jogador recebe movimento suave o bastante sem travar.</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Teste fisico</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>Revalidar longo</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Fechar/reabrir app</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Abrir/fechar 3 vezes.</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Sem processo preso e sem tela branca.</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Teste fisico</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>OK observado</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Pack update</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Verificar/baixar pacote.</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Pronto para Jogar sem barra enganosa.</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Launcher</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>Revalidar depois do split</t>
         </is>
@@ -12267,7 +12556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -14650,7 +14939,7 @@
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>Protagonista (Real Corpo)/Sem nome (Ruiz)</t>
+          <t>Protagonista (Real Corpo)/Grim (Ruiz)</t>
         </is>
       </c>
     </row>
@@ -15387,107 +15676,111 @@
       <c r="L53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>CRITICO - placeholder</t>
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - boss cataclisma</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Placeholder/Teste</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Teste</t>
+          <t>Vhazaryon</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>npc</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Ordem do Vazio Sereno</t>
+          <t>Guardiões do Vulcão</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>Vulcão Selado</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>Nao usar como verdade de campanha; remover, arquivar ou substituir por personagem real.</t>
+          <t>Entidade especial; precisa ficha avancada, fases, mapas, aparencia, VFX/3D, audio e controle de estado.</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>FICHA BASICA</t>
-        </is>
-      </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>falta</t>
-        </is>
-      </c>
-      <c r="J54" s="10" t="inlineStr">
-        <is>
-          <t>falta</t>
+          <t>BOSS CATACLISMA</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>Remover/substituir placeholder por personagem real aprovado</t>
-        </is>
-      </c>
-      <c r="L54" s="8" t="inlineStr"/>
+          <t>Criar ficha avancada de boss: fases, mapas, aparencias, VFX/3D, interludios e controle de fase</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>(F) Guardiões (Vulcão)/Vhazaryon (Dragão FUSHI)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>FOCO - boss cataclisma</t>
+          <t>FOCO - validar mob</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Mob</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Vhazaryon</t>
+          <t>Eco de Kael</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>npc</t>
+          <t>mob</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Guardiões do Vulcão</t>
+          <t>ecos-memoria</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Vulcão Selado</t>
+          <t>Espaco Entre Ecos</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>Entidade especial; precisa ficha avancada, fases, mapas, aparencia, VFX/3D, audio e controle de estado.</t>
+          <t>Criatura simples/encontro; só pode virar OK quando existir na campanha real ou for aprovado como mob canonico.</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>BOSS CATACLISMA</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr">
@@ -15497,14 +15790,242 @@
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>Criar ficha avancada de boss: fases, mapas, aparencias, VFX/3D, interludios e controle de fase</t>
-        </is>
-      </c>
-      <c r="L55" s="8" t="inlineStr">
-        <is>
-          <t>(F) Guardiões (Vulcão)/Vhazaryon (Dragão FUSHI)</t>
-        </is>
-      </c>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+      <c r="L55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - validar mob</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Mob</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Eco de Kairos</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>ecos-memoria</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Espaco Entre Ecos</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>Criatura simples/encontro; só pode virar OK quando existir na campanha real ou for aprovado como mob canonico.</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+      <c r="L56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - validar mob</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Mob</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Eco de Davi</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>ecos-memoria</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Espaco Entre Ecos</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>Criatura simples/encontro; só pode virar OK quando existir na campanha real ou for aprovado como mob canonico.</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+      <c r="L57" s="8" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - validar mob</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Mob</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Eco de Grim</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>ecos-memoria</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Espaco Entre Ecos</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>Criatura simples/encontro; só pode virar OK quando existir na campanha real ou for aprovado como mob canonico.</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+      <c r="L58" s="8" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - validar mob</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Mob</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Eco de Connor</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>ecos-memoria</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Espaco Entre Ecos</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>Criatura simples/encontro; só pode virar OK quando existir na campanha real ou for aprovado como mob canonico.</t>
+        </is>
+      </c>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+      <c r="L59" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15524,7 +16045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X55"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -19527,7 +20048,7 @@
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>Sem nome</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
@@ -19577,7 +20098,7 @@
       </c>
       <c r="X41" s="8" t="inlineStr">
         <is>
-          <t>Protagonista (Real Corpo)/Sem nome (Ruiz)</t>
+          <t>Protagonista (Real Corpo)/Grim (Ruiz)</t>
         </is>
       </c>
     </row>
@@ -20802,44 +21323,44 @@
       <c r="X53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>CRITICO - placeholder</t>
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - boss cataclisma</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Protagonista</t>
+          <t>Boss / NPC</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Teste</t>
+          <t>Vhazaryon</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>FICHA BASICA</t>
+          <t>BOSS CATACLISMA</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>npc</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>Ordem do Vazio Sereno</t>
+          <t>Guardiões do Vulcão</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>Vulcão Selado</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -20847,9 +21368,9 @@
           <t>falta</t>
         </is>
       </c>
-      <c r="J54" s="10" t="inlineStr">
-        <is>
-          <t>falta</t>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
@@ -20859,19 +21380,19 @@
       </c>
       <c r="L54" s="8" t="inlineStr"/>
       <c r="M54" s="8" t="inlineStr"/>
-      <c r="N54" s="10" t="inlineStr">
-        <is>
-          <t>falta estruturar</t>
-        </is>
-      </c>
-      <c r="O54" s="10" t="inlineStr">
-        <is>
-          <t>nao detectado</t>
-        </is>
-      </c>
-      <c r="P54" s="11" t="inlineStr">
-        <is>
-          <t>opcional</t>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O54" s="11" t="inlineStr">
+        <is>
+          <t>requer VFX</t>
+        </is>
+      </c>
+      <c r="P54" s="9" t="inlineStr">
+        <is>
+          <t>necessaria</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
@@ -20880,66 +21401,66 @@
         </is>
       </c>
       <c r="R54" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S54" s="8" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U54" s="8" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="V54" s="8" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="W54" s="8" t="inlineStr">
         <is>
-          <t>Remover/substituir placeholder por personagem real aprovado</t>
-        </is>
-      </c>
-      <c r="X54" s="8" t="inlineStr"/>
+          <t>Criar ficha avancada de boss: fases, mapas, aparencias, VFX/3D, interludios e controle de fase</t>
+        </is>
+      </c>
+      <c r="X54" s="8" t="inlineStr">
+        <is>
+          <t>(F) Guardiões (Vulcão)/Vhazaryon (Dragão FUSHI)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>FOCO - boss cataclisma</t>
+          <t>FOCO - validar mob</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Boss / NPC</t>
+          <t>Mob</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Vhazaryon</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>NPC</t>
-        </is>
-      </c>
+          <t>Eco de Kael</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr"/>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>BOSS CATACLISMA</t>
+          <t>FICHA BASICA</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>npc</t>
+          <t>mob</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>Guardiões do Vulcão</t>
+          <t>ecos-memoria</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>Vulcão Selado</t>
+          <t>Espaco Entre Ecos</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -20947,9 +21468,9 @@
           <t>falta</t>
         </is>
       </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
         </is>
       </c>
       <c r="K55" s="10" t="inlineStr">
@@ -20964,14 +21485,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="O55" s="11" t="inlineStr">
-        <is>
-          <t>requer VFX</t>
-        </is>
-      </c>
-      <c r="P55" s="9" t="inlineStr">
-        <is>
-          <t>necessaria</t>
+      <c r="O55" s="10" t="inlineStr">
+        <is>
+          <t>nao detectado</t>
+        </is>
+      </c>
+      <c r="P55" s="11" t="inlineStr">
+        <is>
+          <t>opcional</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
@@ -20980,30 +21501,410 @@
         </is>
       </c>
       <c r="R55" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S55" s="8" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U55" s="8" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="V55" s="8" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="W55" s="8" t="inlineStr">
         <is>
-          <t>Criar ficha avancada de boss: fases, mapas, aparencias, VFX/3D, interludios e controle de fase</t>
-        </is>
-      </c>
-      <c r="X55" s="8" t="inlineStr">
-        <is>
-          <t>(F) Guardiões (Vulcão)/Vhazaryon (Dragão FUSHI)</t>
-        </is>
-      </c>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+      <c r="X55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - validar mob</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Mob</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Eco de Kairos</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr"/>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>ecos-memoria</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Espaco Entre Ecos</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>nao detectada</t>
+        </is>
+      </c>
+      <c r="L56" s="8" t="inlineStr"/>
+      <c r="M56" s="8" t="inlineStr"/>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O56" s="10" t="inlineStr">
+        <is>
+          <t>nao detectado</t>
+        </is>
+      </c>
+      <c r="P56" s="11" t="inlineStr">
+        <is>
+          <t>opcional</t>
+        </is>
+      </c>
+      <c r="Q56" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="8" t="inlineStr">
+        <is>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+      <c r="X56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - validar mob</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Mob</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Eco de Davi</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr"/>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>ecos-memoria</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Espaco Entre Ecos</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="inlineStr">
+        <is>
+          <t>nao detectada</t>
+        </is>
+      </c>
+      <c r="L57" s="8" t="inlineStr"/>
+      <c r="M57" s="8" t="inlineStr"/>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O57" s="10" t="inlineStr">
+        <is>
+          <t>nao detectado</t>
+        </is>
+      </c>
+      <c r="P57" s="11" t="inlineStr">
+        <is>
+          <t>opcional</t>
+        </is>
+      </c>
+      <c r="Q57" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="8" t="inlineStr">
+        <is>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+      <c r="X57" s="8" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - validar mob</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Mob</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Eco de Grim</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr"/>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>ecos-memoria</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Espaco Entre Ecos</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>nao detectada</t>
+        </is>
+      </c>
+      <c r="L58" s="8" t="inlineStr"/>
+      <c r="M58" s="8" t="inlineStr"/>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O58" s="10" t="inlineStr">
+        <is>
+          <t>nao detectado</t>
+        </is>
+      </c>
+      <c r="P58" s="11" t="inlineStr">
+        <is>
+          <t>opcional</t>
+        </is>
+      </c>
+      <c r="Q58" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="8" t="inlineStr">
+        <is>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+      <c r="X58" s="8" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - validar mob</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Mob</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Eco de Connor</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr"/>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>ecos-memoria</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Espaco Entre Ecos</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="inlineStr">
+        <is>
+          <t>nao detectada</t>
+        </is>
+      </c>
+      <c r="L59" s="8" t="inlineStr"/>
+      <c r="M59" s="8" t="inlineStr"/>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O59" s="10" t="inlineStr">
+        <is>
+          <t>nao detectado</t>
+        </is>
+      </c>
+      <c r="P59" s="11" t="inlineStr">
+        <is>
+          <t>opcional</t>
+        </is>
+      </c>
+      <c r="Q59" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="8" t="inlineStr">
+        <is>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+      <c r="X59" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -21023,7 +21924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -21514,7 +22415,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Sem nome</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -21550,7 +22451,7 @@
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>Protagonista (Real Corpo)/Sem nome (Ruiz)</t>
+          <t>Protagonista (Real Corpo)/Grim (Ruiz)</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
@@ -21561,59 +22462,6 @@
       <c r="O10" s="8" t="inlineStr">
         <is>
           <t>player-ruiz-sem-nome</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>CRITICO - placeholder</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Consciência/player individual</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>falta</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>falta</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>Remover/substituir personagem de teste antes de usar como planejamento real.</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
-      <c r="O11" s="8" t="inlineStr">
-        <is>
-          <t>character-dc758c81-53f2-4cea-953e-ee205f8586a2</t>
         </is>
       </c>
     </row>
@@ -21635,7 +22483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -21742,17 +22590,17 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Entrar como Mestre, mapa e tokens aparecem, sem readiness preso.</t>
+          <t>Entrar como Mestre, mapa e tokens aparecem, sem readiness preso; Ctrl+A recupera apenas a arte visual sem trocar mapa, tokens, camera ou sessao.</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Teste fisico recente estavel.</t>
+          <t>Alpha.88: smoke:ui e smoke:release aprovados; smoke:interludes confirmou epoch visual 0 -&gt; 1 com o mesmo mapa e o mesmo conjunto de tokens.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Manter smoke:ui e smoke:release.</t>
+          <t>Testar Ctrl+A fisicamente somente se surgir imagem branca; manter smoke:ui e smoke:release.</t>
         </is>
       </c>
     </row>
@@ -21774,17 +22622,17 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Dados, ficha, chat/rolagem, regua e visibilidade sincronizam nos dois sentidos.</t>
+          <t>Dados, ficha, chat/rolagem, regua e visibilidade sincronizam nos dois sentidos; sair da Mesa sem fechar o app nao pede novo aceite.</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Teste fisico com 2 jogadores respondeu bem.</t>
+          <t>Alpha.85 valida socket novo da mesma instancia, instancia estrangeira pendente, 5 jogadores, 5 ciclos de soak e reentrada real no app empacotado.</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Soak maior antes de promover release.</t>
+          <t>Manter smoke:multiplayer, smoke:multiplayer:soak e smoke:release como gate obrigatorio.</t>
         </is>
       </c>
     </row>
@@ -21796,27 +22644,27 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Dados</t>
+          <t>Multiplayer</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Fila, cooldown e idempotencia</t>
+          <t>Reentrada da sessao aceita</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Rolagens rapidas nao duplicam por retry/lag.</t>
+          <t>Fluxo/Livro/Multiplayer e troca de socket nao exigem novo aceite enquanto a mesma instancia do app estiver aberta; fechar, recusar ou expulsar revoga a sessao.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Usuario testou e nao bugou.</t>
+          <t>Protocolo v3 vincula a concessao ao playerId + clientInstanceId; smoke:multiplayer e smoke:release cobrem reconexao real e revogacao.</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Manter smoke:multiplayer.</t>
+          <t>Revalidar fisicamente em dois PCs na proxima sessao.</t>
         </is>
       </c>
     </row>
@@ -21828,27 +22676,27 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Regua</t>
+          <t>Ficha</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Regua multiplayer</t>
+          <t>Ficha canonica bidirecional</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Linha e label aparecem sem flicker forte para Mestre e Jogador.</t>
+          <t>Mestre atribui skill/build e jogador recebe; jogador altera campos permitidos e Mestre recebe sem apagar campos canonicos.</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Reforcada e testada depois do bug.</t>
+          <t>Alpha.87 envia patches do jogador e protege skills, rituais, builds, permissoes e corpo compartilhado; o smoke multiplayer confirma Vida efetiva 17/17 (base 10 + Build 7) no Jogador e preserva o maximo apos o patch Jogador &gt; Mestre.</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Revalidar em sessao longa.</t>
+          <t>Nao aceitar build futura sem o gate Mestre &gt; Jogador e Jogador &gt; Mestre.</t>
         </is>
       </c>
     </row>
@@ -21860,27 +22708,27 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Tokens</t>
+          <t>Ficha</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Controle e visual de token</t>
+          <t>Efeitos e marcas canonicos</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Mestre move; jogador nao move; borda/visibilidade nao usa transparencia feia.</t>
+          <t>Origem ve Seus efeitos; alvo ve Efeitos aplicados; somente origem autorizada ou Mestre cancela; jogador nao recebe IDs internos.</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Fluxo observado como responsivo.</t>
+          <t>Alpha.88: Analise Cirurgica usa efeito estruturado com origem/alvo; smoke:multiplayer validou cancelamento Jogador &gt; Mestre, ACK idempotente, persistencia canonica e sanitizacao publica.</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Revalidar com 5 jogadores.</t>
+          <t>Playtest fisico com Davi aplicando e cancelando a marca em outro jogador.</t>
         </is>
       </c>
     </row>
@@ -21892,27 +22740,27 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Interludios</t>
+          <t>Eventos</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>MUN e mapas com thumb/topdown</t>
+          <t>EVE publico efemero</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Abrir mapa nao fica branco/preto; interludio tem thumb e fallback coerente.</t>
+          <t>Sorteio atual aparece aos jogadores e pode ser dispensado; backlog e ultimo roll nao reaparecem ao voltar para a mesa.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>119 interludios automaticos OK e 0 thumbs vazias.</t>
+          <t>Alpha.87 cobre transmissao depois da reconexao, descarte pelo jogador e ausencia de replay nos smokes de eventos, multiplayer e release real.</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Revisao artistica por cena.</t>
+          <t>Todo novo EVE publico precisa de teste empacotado com visao de jogador.</t>
         </is>
       </c>
     </row>
@@ -21924,27 +22772,27 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Base/MUN</t>
+          <t>Dados</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Liberar Base/MUN e preparar mapa</t>
+          <t>Fila, cooldown e idempotencia</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Mestre prepara sem puxar jogadores; ativar leva jogadores ao mapa correto.</t>
+          <t>Rolagens rapidas nao duplicam por retry/lag.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Corrigido e sem bug aparente depois.</t>
+          <t>Usuario testou e nao bugou.</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Revalidar no release empacotado.</t>
+          <t>Manter smoke:multiplayer.</t>
         </is>
       </c>
     </row>
@@ -21956,27 +22804,315 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
+          <t>Regua</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Regua multiplayer</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Linha e label aparecem sem flicker forte para Mestre e Jogador.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Reforcada e testada depois do bug.</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Revalidar em sessao longa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Tokens</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Controle e visual de token</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Mestre move; jogador nao move; borda/visibilidade nao usa transparencia feia.</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Fluxo observado como responsivo.</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Revalidar com 5 jogadores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Interludios</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>MUN e mapas com thumb/topdown</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Abrir mapa nao fica branco/preto; interludio tem thumb e fallback coerente.</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Alpha.88: 121/121 interludios automaticos possuem fonte valida no pacote, 0 thumbs vazias; Estatuas do Litoral usa a imagem semantica do MUN; cinco ciclos empacotados e 0 falhas de rede.</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Revisao artistica por cena; manter a auditoria semantica antes de cada release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Base/MUN</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Liberar Base/MUN e preparar mapa</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Mestre prepara sem puxar jogadores; ativar leva jogadores ao mapa correto.</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Alpha.84 validada no release empacotado: preparar mapa, voltar ao submapa e liberar Base passaram no smoke:release:deep.</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Revalidar apenas se o protocolo MUN/Base mudar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
           <t>Release</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Build empacotado real</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>release/win-unpacked abre e smokes rodam isolados.</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Baseline alpha.83 estavel.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Nao promover conteudo sem smoke:release.</t>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Alpha.87 empacotada em release/win-unpacked e instaladores; build, lint, release:assets, smoke:ui, smoke:multiplayer, smoke:release e smoke:release:deep 11/11 aprovados.</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Nao promover conteudo sem smoke:release e o gate especifico da area alterada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Livros</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Livro do Jogador e Livro do Mestre</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Jogador consulta regras publicas no Fluxo e na Mesa sem ver reencarnacao/progressao oculta; Mestre consulta escudo e compendio real; PDFs passam auditoria visual e de sigilo.</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Combat V2: 15 capitulos publicos, 18 capitulos do Mestre, PDF Jogador 23 paginas, PDF Mestre 363 paginas; auditoria visual, sigilo e bordas aprovada.</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Atualizar src/data/rulebook a cada decisao aprovada; rodar books:build, books:audit e smoke:rulebooks:release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Combate</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Combat V2 - defesa, critico e turnos</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>CA e passiva; Bloqueio usa Fortitude (0/5/10/15); Esquiva fixa usa CA atual + AGI + Reflexos como Reacao; critico dobra apenas dados; turnos mostram Principal, Curta, Movimento, Reacao e manobras.</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Alpha.88: 56 fichas Combat V2; fluxo visual ficha -&gt; Dados de Combate -&gt; dado -&gt; Resolver -&gt; confirmacao; recibo privado, impacto, marca e queda protegidos por smokes runtime, UI e multiplayer.</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Playtest fisico curto Mestre/Jogador para confirmar leitura e ritmo; manter Veyra e demais lacunas de conteudo como alerta ate revisao canonica do Mestre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Builds</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Catalogo, raridades e vinculo BUI</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>48 itens, cinco raridades, conjuntos de NPC e vinculo canonico funcionam sem alterar lore ou aceitar sobrescrita do Jogador.</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Baseline canonico aprovado por smoke:builds: 48 itens, 240 raridades e 41 conjuntos 8/8. Alpha.87 separa valor base do efetivo: editar base reaplica o total da build e remover item restaura a base sem residuo; smoke:ui e multiplayer protegem o contrato.</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Em teste real: editar a Vida base de Connor para 20, confirmar 34 com Build +14, remover a build e confirmar retorno a 20. Ajustar numeros somente com evidencia de playtest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Eventos</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Hub EVE e ciclo de vida</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Mestre ativa dois ou mais eventos, desativa cada um isoladamente e a Mesa volta ao estado-base sem apagar progresso.</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Treino Inicial e Sorteio Raridade Build passaram em build, smoke:events, smoke:training:ui, smoke:multiplayer, smoke:release e smoke:release:deep 11/11; campos privados foram removidos do payload do Jogador e a revelacao agora fecha por clique sem alterar ficha/EVE.</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Manter em teste real; todo evento novo deve seguir FUSHI_EVENT_SYSTEM_V1 e ganhar smoke proprio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Treinamento</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Circuito do Centro no Campo de Treinamento</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Mestre ativa/desativa pelo EVE ou MUN; cinco jogadores veem quests e progresso; somente Mestre ve DT e aplica Marcas, Contratempos e Segundo Sino.</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>smoke:training, smoke:training:ui e smoke:multiplayer aprovados; desativacao remove o painel em Mestre/Jogador, preserva a Marca e permite retomar.</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Teste real na proxima sessao; refinamento narrativo e habilidades continuam dependendo de aprovacao do Mestre.</t>
         </is>
       </c>
     </row>
@@ -23232,9 +24368,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -23258,10 +24394,10 @@
         </is>
       </c>
       <c r="F5" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>6</v>
@@ -23567,7 +24703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -23700,10 +24836,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" s="8" t="n">
         <v>0</v>
@@ -24115,6 +25251,68 @@
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>OK base</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Mundo dos Sonhos / Subconsciente do Fragmentado</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>mundo_interno_fragmentado</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>variavel</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>fragmentado</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>memorias, ecos de consciencia, fios de vinculo</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>Manter MUN/app como fonte para novos mapas e interludios.</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>Camada interna fora dos biomas fisicos; nao e sonho literal, mas a forma como o Fragmentado ve lembrancas, ecos e vinculos de consciencia.</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>Use como ponto isolado do MUN para sessoes solo, conversas internas e cenas de memoria compartilhada.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -24538,7 +25736,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Ir NPC por NPC quando for produzir cena.</t>
+          <t>Solo de Kael implementado no Mundo dos Sonhos do Fragmentado, com mobs Eco de Kael/Kairos/Davi/Grim/Connor; usar como pista de corpo/alma sem revelar verdade inteira.</t>
         </is>
       </c>
     </row>
@@ -24565,7 +25763,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Validar Lobo Cinzento, Lobo Marcado por FUSHI e Eco de Liora.</t>
+          <t>Lobo Cinzento (8 Vida) e Lobo Marcado por FUSHI (14 Vida) ja usam Combat V2; testar a Clareira com grupo real antes de criar outro mob.</t>
         </is>
       </c>
     </row>
@@ -24619,7 +25817,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Organizar por bioma quando for criar cena.</t>
+          <t>Sessao 3 comeca com Fragmentado ferido voltando da Clareira; o solo de Kael fica ligado ao ponto MUN Mundo dos Sonhos do Fragmentado, fora dos biomas fisicos, enquanto Orian/Cartoteca, Campo de Treino, Nilo/Riacho e corpo/alma seguem como ganchos, nao trilhos.</t>
         </is>
       </c>
     </row>
@@ -24722,7 +25920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -25124,7 +26322,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Sem nome</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -25156,52 +26354,6 @@
       <c r="L10" s="8" t="inlineStr">
         <is>
           <t>Manter vínculo app + corpo real + premissa; completar ficha no app quando a lore virar mecanica.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>CRITICO - placeholder</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Consciência/player individual</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>falta</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>falta</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr"/>
-      <c r="J11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>Remover/substituir personagem de teste antes de usar como planejamento real.</t>
         </is>
       </c>
     </row>
@@ -25223,7 +26375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -27762,106 +28914,106 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>CRITICO - placeholder</t>
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - boss cataclisma</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Placeholder/Teste</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Teste</t>
+          <t>Vhazaryon</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>npc</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Ordem do Vazio Sereno</t>
+          <t>Guardiões do Vulcão</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>Vulcão Selado</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>Nao usar como verdade de campanha; remover, arquivar ou substituir por personagem real.</t>
+          <t>Entidade especial; precisa ficha avancada, fases, mapas, aparencia, VFX/3D, audio e controle de estado.</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>FICHA BASICA</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>falta</t>
-        </is>
-      </c>
-      <c r="J48" s="10" t="inlineStr">
-        <is>
-          <t>falta</t>
+          <t>BOSS CATACLISMA</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>Remover/substituir placeholder por personagem real aprovado</t>
+          <t>Criar ficha avancada de boss: fases, mapas, aparencias, VFX/3D, interludios e controle de fase</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>FOCO - boss cataclisma</t>
+          <t>FOCO - validar mob</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Mob</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Vhazaryon</t>
+          <t>Eco de Kael</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>npc</t>
+          <t>mob</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Guardiões do Vulcão</t>
+          <t>ecos-memoria</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Vulcão Selado</t>
+          <t>Espaco Entre Ecos</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>Entidade especial; precisa ficha avancada, fases, mapas, aparencia, VFX/3D, audio e controle de estado.</t>
+          <t>Criatura simples/encontro; só pode virar OK quando existir na campanha real ou for aprovado como mob canonico.</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>BOSS CATACLISMA</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
@@ -27871,7 +29023,235 @@
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>Criar ficha avancada de boss: fases, mapas, aparencias, VFX/3D, interludios e controle de fase</t>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - validar mob</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Mob</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Eco de Kairos</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>ecos-memoria</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Espaco Entre Ecos</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>Criatura simples/encontro; só pode virar OK quando existir na campanha real ou for aprovado como mob canonico.</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - validar mob</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Mob</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Eco de Davi</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>ecos-memoria</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Espaco Entre Ecos</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>Criatura simples/encontro; só pode virar OK quando existir na campanha real ou for aprovado como mob canonico.</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - validar mob</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Mob</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Eco de Grim</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>ecos-memoria</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Espaco Entre Ecos</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>Criatura simples/encontro; só pode virar OK quando existir na campanha real ou for aprovado como mob canonico.</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>FOCO - validar mob</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Mob</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Eco de Connor</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>ecos-memoria</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Espaco Entre Ecos</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>Criatura simples/encontro; só pode virar OK quando existir na campanha real ou for aprovado como mob canonico.</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>FICHA BASICA</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>falta</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>Confirmar se criatura existe na campanha real; nao marcar como OK sem lore, ficha ou aprovacao.</t>
         </is>
       </c>
     </row>
@@ -28946,7 +30326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -29053,10 +30433,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>0</v>
@@ -29402,6 +30782,55 @@
       <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Observacao, bases moveis, investigacao e caminhos discretos da Ordem do Veu Cinza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>OK base</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Mundo dos Sonhos / Subconsciente do Fragmentado</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>variavel</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>fragmentado</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>memorias, ecos de consciencia, fios de vinculo</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Manter MUN/app como fonte para novos mapas e interludios.</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Camada interna fora dos biomas fisicos; nao e sonho literal, mas a forma como o Fragmentado ve lembrancas, ecos e vinculos de consciencia.</t>
         </is>
       </c>
     </row>
@@ -29423,7 +30852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -29745,6 +31174,70 @@
       <c r="F13" s="8" t="inlineStr">
         <is>
           <t>perf:release em low/balanced/ultra</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Protocolo</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Item de build</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>raridade, ganho, perda, passiva simples, origem MUN, log e estado permanente</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>preview claro de tradeoff; VFX/audio apenas se a regra pedir</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Simuladores offline + smoke:multiplayer + release empacotado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Protocolo</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Acao de combate transacional</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>automation.combat com acao, teste, dano, alcance, resolucao, falha e reacao quando aplicaveis</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>ficha prepara; Dados de Combate escolhe alvo; Resolver abre depois do dado; impacto e recibo sanitizados</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>smoke:combat-runtime + smoke:combat-flow:ui + smoke:multiplayer + smoke:release</t>
         </is>
       </c>
     </row>
@@ -29825,27 +31318,27 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ESTAVEL</t>
+          <t>ALPHA.85 OK</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>119 OK</t>
+          <t>121 OK</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>8 biomas</t>
+          <t>9 biomas</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>7 fichas</t>
+          <t>6 fichas</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>51 linhas</t>
+          <t>55 linhas</t>
         </is>
       </c>
     </row>
@@ -29880,16 +31373,16 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>4366.0 MiB</t>
+          <t>4422.7 MiB</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>3074.1 MiB</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>1</v>
+          <t>3120.6 MiB</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -29946,14 +31439,14 @@
           <t>0 pronto</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>7 pontos</t>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>6 pontos</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>328.8 MiB</t>
+          <t>349.2 MiB</t>
         </is>
       </c>
     </row>
@@ -30153,19 +31646,19 @@
     <hyperlink ref="E4" location="'Mundo_Biomas'!A1" display="Mundo / biomas"/>
     <hyperlink ref="G4" location="'Protagonistas'!A1" display="Protagonistas"/>
     <hyperlink ref="I4" location="'Personagens_Campanha'!A1" display="Personagens"/>
-    <hyperlink ref="A5" location="'Checklist_Teste'!A1" display="ESTAVEL"/>
-    <hyperlink ref="C5" location="'MUN_Assets'!A1" display="119 OK"/>
-    <hyperlink ref="E5" location="'Mundo_Biomas'!A1" display="8 biomas"/>
-    <hyperlink ref="G5" location="'Protagonistas'!A1" display="7 fichas"/>
-    <hyperlink ref="I5" location="'Personagens_Campanha'!A1" display="51 linhas"/>
+    <hyperlink ref="A5" location="'Checklist_Teste'!A1" display="ALPHA.85 OK"/>
+    <hyperlink ref="C5" location="'MUN_Assets'!A1" display="121 OK"/>
+    <hyperlink ref="E5" location="'Mundo_Biomas'!A1" display="9 biomas"/>
+    <hyperlink ref="G5" location="'Protagonistas'!A1" display="6 fichas"/>
+    <hyperlink ref="I5" location="'Personagens_Campanha'!A1" display="55 linhas"/>
     <hyperlink ref="A8" location="'Core_vs_Pack'!A1" display="Pack campanha"/>
     <hyperlink ref="C8" location="'Peso_Assets'!A1" display="Economia possivel"/>
     <hyperlink ref="E8" location="'NPC_Mecanicas'!A1" display="Criticos reais"/>
     <hyperlink ref="G8" location="'Bosses_Fases'!A1" display="Bosses / fases"/>
     <hyperlink ref="I8" location="'Bosses_Fases'!A1" display="Vhazaryon"/>
-    <hyperlink ref="A9" location="'Core_vs_Pack'!A1" display="4366.0 MiB"/>
-    <hyperlink ref="C9" location="'Peso_Assets'!A1" display="3074.1 MiB"/>
-    <hyperlink ref="E9" location="'NPC_Mecanicas'!A1" display="1"/>
+    <hyperlink ref="A9" location="'Core_vs_Pack'!A1" display="4422.7 MiB"/>
+    <hyperlink ref="C9" location="'Peso_Assets'!A1" display="3120.6 MiB"/>
+    <hyperlink ref="E9" location="'NPC_Mecanicas'!A1" display="0"/>
     <hyperlink ref="G9" location="'Bosses_Fases'!A1" display="15 foco"/>
     <hyperlink ref="I9" location="'Bosses_Fases'!A1" display="FOCO - boss cataclisma"/>
     <hyperlink ref="A12" location="'Faccoes'!A1" display="Faccoes"/>
@@ -30176,8 +31669,8 @@
     <hyperlink ref="A13" location="'Faccoes'!A1" display="6 grupos"/>
     <hyperlink ref="C13" location="'Conteudo_Futuro'!A1" display="5 vazios"/>
     <hyperlink ref="E13" location="'Conteudo_Futuro'!A1" display="0 pronto"/>
-    <hyperlink ref="G13" location="'Divergencias'!A1" display="7 pontos"/>
-    <hyperlink ref="I13" location="'Core_vs_Pack'!A1" display="328.8 MiB"/>
+    <hyperlink ref="G13" location="'Divergencias'!A1" display="6 pontos"/>
+    <hyperlink ref="I13" location="'Core_vs_Pack'!A1" display="349.2 MiB"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
+++ b/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
@@ -524,8 +524,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ControleRegrasTable" displayName="ControleRegrasTable" ref="G13:G28" headerRowCount="1">
-  <autoFilter ref="G13:G28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ControleRegrasTable" displayName="ControleRegrasTable" ref="G13:G29" headerRowCount="1">
+  <autoFilter ref="G13:G29"/>
   <tableColumns count="1">
     <tableColumn id="7" name="Regra"/>
   </tableColumns>
@@ -643,8 +643,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="AppBaseChecklistTable" displayName="AppBaseChecklistTable" ref="A4:F22" headerRowCount="1">
-  <autoFilter ref="A4:F22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="AppBaseChecklistTable" displayName="AppBaseChecklistTable" ref="A4:F23" headerRowCount="1">
+  <autoFilter ref="A4:F23"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Area"/>
@@ -1059,7 +1059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1442,6 +1442,13 @@
       <c r="G28" s="8" t="inlineStr">
         <is>
           <t>Combat V2 e a fonte ativa para CA, Bloqueio, Esquiva, critico, manobras, escala de mobs e simulacao; FUSHI_COMBAT_V2.md prevalece sobre regra V1 conflitante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Estagios/Fases usam uma unica ficha canonica ativa; catalogo privado do Mestre fica em snapshots nao recursivos, Jogador recebe apenas fase ativa e revision, e toda troca precisa de VFX idempotente e teste Mestre &gt; Jogador.</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -22703,7 +22710,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK tecnico</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -22713,22 +22720,22 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Efeitos e marcas canonicos</t>
+          <t>Estagios/Fases da ficha</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Origem ve Seus efeitos; alvo ve Efeitos aplicados; somente origem autorizada ou Mestre cancela; jogador nao recebe IDs internos.</t>
+          <t>Mestre cria, edita, renomeia, troca e arquiva fases; a fase ativa continua sendo a ficha canonica e jogadores recebem somente fase ativa, imagem atual e revision.</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Alpha.88: Analise Cirurgica usa efeito estruturado com origem/alvo; smoke:multiplayer validou cancelamento Jogador &gt; Mestre, ACK idempotente, persistencia canonica e sanitizacao publica.</t>
+          <t>Alpha.88: smoke:stages, smoke:multiplayer, smoke:ui, smoke:release e smoke:release:deep passaram; release empacotado criou, ativou e retornou de uma fase sem vazar catalogo.</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Playtest fisico com Davi aplicando e cancelando a marca em outro jogador.</t>
+          <t>Playtest fisico com Mestre + Jogador: trocar fase, editar imagem/vida, confirmar VFX unico e retorno sem novo aceite.</t>
         </is>
       </c>
     </row>
@@ -22740,27 +22747,27 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Eventos</t>
+          <t>Ficha</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>EVE publico efemero</t>
+          <t>Efeitos e marcas canonicos</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Sorteio atual aparece aos jogadores e pode ser dispensado; backlog e ultimo roll nao reaparecem ao voltar para a mesa.</t>
+          <t>Origem ve Seus efeitos; alvo ve Efeitos aplicados; somente origem autorizada ou Mestre cancela; jogador nao recebe IDs internos.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Alpha.87 cobre transmissao depois da reconexao, descarte pelo jogador e ausencia de replay nos smokes de eventos, multiplayer e release real.</t>
+          <t>Alpha.88: Analise Cirurgica usa efeito estruturado com origem/alvo; smoke:multiplayer validou cancelamento Jogador &gt; Mestre, ACK idempotente, persistencia canonica e sanitizacao publica.</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Todo novo EVE publico precisa de teste empacotado com visao de jogador.</t>
+          <t>Playtest fisico com Davi aplicando e cancelando a marca em outro jogador.</t>
         </is>
       </c>
     </row>
@@ -22772,27 +22779,27 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Dados</t>
+          <t>Eventos</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Fila, cooldown e idempotencia</t>
+          <t>EVE publico efemero</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Rolagens rapidas nao duplicam por retry/lag.</t>
+          <t>Sorteio atual aparece aos jogadores e pode ser dispensado; backlog e ultimo roll nao reaparecem ao voltar para a mesa.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Usuario testou e nao bugou.</t>
+          <t>Alpha.87 cobre transmissao depois da reconexao, descarte pelo jogador e ausencia de replay nos smokes de eventos, multiplayer e release real.</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Manter smoke:multiplayer.</t>
+          <t>Todo novo EVE publico precisa de teste empacotado com visao de jogador.</t>
         </is>
       </c>
     </row>
@@ -22804,27 +22811,27 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Regua</t>
+          <t>Dados</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Regua multiplayer</t>
+          <t>Fila, cooldown e idempotencia</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Linha e label aparecem sem flicker forte para Mestre e Jogador.</t>
+          <t>Rolagens rapidas nao duplicam por retry/lag.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Reforcada e testada depois do bug.</t>
+          <t>Usuario testou e nao bugou.</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Revalidar em sessao longa.</t>
+          <t>Manter smoke:multiplayer.</t>
         </is>
       </c>
     </row>
@@ -22836,27 +22843,27 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Tokens</t>
+          <t>Regua</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Controle e visual de token</t>
+          <t>Regua multiplayer</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Mestre move; jogador nao move; borda/visibilidade nao usa transparencia feia.</t>
+          <t>Linha e label aparecem sem flicker forte para Mestre e Jogador.</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Fluxo observado como responsivo.</t>
+          <t>Reforcada e testada depois do bug.</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>Revalidar com 5 jogadores.</t>
+          <t>Revalidar em sessao longa.</t>
         </is>
       </c>
     </row>
@@ -22868,27 +22875,27 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Interludios</t>
+          <t>Tokens</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>MUN e mapas com thumb/topdown</t>
+          <t>Controle e visual de token</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Abrir mapa nao fica branco/preto; interludio tem thumb e fallback coerente.</t>
+          <t>Mestre move; jogador nao move; borda/visibilidade nao usa transparencia feia.</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Alpha.88: 121/121 interludios automaticos possuem fonte valida no pacote, 0 thumbs vazias; Estatuas do Litoral usa a imagem semantica do MUN; cinco ciclos empacotados e 0 falhas de rede.</t>
+          <t>Fluxo observado como responsivo.</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Revisao artistica por cena; manter a auditoria semantica antes de cada release.</t>
+          <t>Revalidar com 5 jogadores.</t>
         </is>
       </c>
     </row>
@@ -22900,27 +22907,27 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Base/MUN</t>
+          <t>Interludios</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Liberar Base/MUN e preparar mapa</t>
+          <t>MUN e mapas com thumb/topdown</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Mestre prepara sem puxar jogadores; ativar leva jogadores ao mapa correto.</t>
+          <t>Abrir mapa nao fica branco/preto; interludio tem thumb e fallback coerente.</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Alpha.84 validada no release empacotado: preparar mapa, voltar ao submapa e liberar Base passaram no smoke:release:deep.</t>
+          <t>Alpha.88: 121/121 interludios automaticos possuem fonte valida no pacote, 0 thumbs vazias; Estatuas do Litoral usa a imagem semantica do MUN; cinco ciclos empacotados e 0 falhas de rede.</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Revalidar apenas se o protocolo MUN/Base mudar.</t>
+          <t>Revisao artistica por cena; manter a auditoria semantica antes de cada release.</t>
         </is>
       </c>
     </row>
@@ -22932,27 +22939,27 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Base/MUN</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Build empacotado real</t>
+          <t>Liberar Base/MUN e preparar mapa</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>release/win-unpacked abre e smokes rodam isolados.</t>
+          <t>Mestre prepara sem puxar jogadores; ativar leva jogadores ao mapa correto.</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Alpha.87 empacotada em release/win-unpacked e instaladores; build, lint, release:assets, smoke:ui, smoke:multiplayer, smoke:release e smoke:release:deep 11/11 aprovados.</t>
+          <t>Alpha.84 validada no release empacotado: preparar mapa, voltar ao submapa e liberar Base passaram no smoke:release:deep.</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Nao promover conteudo sem smoke:release e o gate especifico da area alterada.</t>
+          <t>Revalidar apenas se o protocolo MUN/Base mudar.</t>
         </is>
       </c>
     </row>
@@ -22964,59 +22971,59 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Build empacotado real</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>release/win-unpacked abre e smokes rodam isolados.</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Alpha.87 empacotada em release/win-unpacked e instaladores; build, lint, release:assets, smoke:ui, smoke:multiplayer, smoke:release e smoke:release:deep 11/11 aprovados.</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Nao promover conteudo sem smoke:release e o gate especifico da area alterada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
           <t>Livros</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Livro do Jogador e Livro do Mestre</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Jogador consulta regras publicas no Fluxo e na Mesa sem ver reencarnacao/progressao oculta; Mestre consulta escudo e compendio real; PDFs passam auditoria visual e de sigilo.</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Combat V2: 15 capitulos publicos, 18 capitulos do Mestre, PDF Jogador 23 paginas, PDF Mestre 363 paginas; auditoria visual, sigilo e bordas aprovada.</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Atualizar src/data/rulebook a cada decisao aprovada; rodar books:build, books:audit e smoke:rulebooks:release.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>FOCO</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Combate</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Combat V2 - defesa, critico e turnos</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>CA e passiva; Bloqueio usa Fortitude (0/5/10/15); Esquiva fixa usa CA atual + AGI + Reflexos como Reacao; critico dobra apenas dados; turnos mostram Principal, Curta, Movimento, Reacao e manobras.</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Alpha.88: 56 fichas Combat V2; fluxo visual ficha -&gt; Dados de Combate -&gt; dado -&gt; Resolver -&gt; confirmacao; recibo privado, impacto, marca e queda protegidos por smokes runtime, UI e multiplayer.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Playtest fisico curto Mestre/Jogador para confirmar leitura e ritmo; manter Veyra e demais lacunas de conteudo como alerta ate revisao canonica do Mestre.</t>
         </is>
       </c>
     </row>
@@ -23028,59 +23035,59 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
+          <t>Combate</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Combat V2 - defesa, critico e turnos</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>CA e passiva; Bloqueio usa Fortitude (0/5/10/15); Esquiva fixa usa CA atual + AGI + Reflexos como Reacao; critico dobra apenas dados; turnos mostram Principal, Curta, Movimento, Reacao e manobras.</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Alpha.88: 56 fichas Combat V2; fluxo visual ficha -&gt; Dados de Combate -&gt; dado -&gt; Resolver -&gt; confirmacao; recibo privado, impacto, marca e queda protegidos por smokes runtime, UI e multiplayer.</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Playtest fisico curto Mestre/Jogador para confirmar leitura e ritmo; manter Veyra e demais lacunas de conteudo como alerta ate revisao canonica do Mestre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
           <t>Builds</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Catalogo, raridades e vinculo BUI</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>48 itens, cinco raridades, conjuntos de NPC e vinculo canonico funcionam sem alterar lore ou aceitar sobrescrita do Jogador.</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Baseline canonico aprovado por smoke:builds: 48 itens, 240 raridades e 41 conjuntos 8/8. Alpha.87 separa valor base do efetivo: editar base reaplica o total da build e remover item restaura a base sem residuo; smoke:ui e multiplayer protegem o contrato.</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Em teste real: editar a Vida base de Connor para 20, confirmar 34 com Build +14, remover a build e confirmar retorno a 20. Ajustar numeros somente com evidencia de playtest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Eventos</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Hub EVE e ciclo de vida</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Mestre ativa dois ou mais eventos, desativa cada um isoladamente e a Mesa volta ao estado-base sem apagar progresso.</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Treino Inicial e Sorteio Raridade Build passaram em build, smoke:events, smoke:training:ui, smoke:multiplayer, smoke:release e smoke:release:deep 11/11; campos privados foram removidos do payload do Jogador e a revelacao agora fecha por clique sem alterar ficha/EVE.</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Manter em teste real; todo evento novo deve seguir FUSHI_EVENT_SYSTEM_V1 e ganhar smoke proprio.</t>
         </is>
       </c>
     </row>
@@ -23092,25 +23099,57 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
+          <t>Eventos</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Hub EVE e ciclo de vida</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Mestre ativa dois ou mais eventos, desativa cada um isoladamente e a Mesa volta ao estado-base sem apagar progresso.</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Treino Inicial e Sorteio Raridade Build passaram em build, smoke:events, smoke:training:ui, smoke:multiplayer, smoke:release e smoke:release:deep 11/11; campos privados foram removidos do payload do Jogador e a revelacao agora fecha por clique sem alterar ficha/EVE.</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Manter em teste real; todo evento novo deve seguir FUSHI_EVENT_SYSTEM_V1 e ganhar smoke proprio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
           <t>Treinamento</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Circuito do Centro no Campo de Treinamento</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Mestre ativa/desativa pelo EVE ou MUN; cinco jogadores veem quests e progresso; somente Mestre ve DT e aplica Marcas, Contratempos e Segundo Sino.</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>smoke:training, smoke:training:ui e smoke:multiplayer aprovados; desativacao remove o painel em Mestre/Jogador, preserva a Marca e permite retomar.</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>Teste real na proxima sessao; refinamento narrativo e habilidades continuam dependendo de aprovacao do Mestre.</t>
         </is>

--- a/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
+++ b/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
@@ -2,29 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controle" sheetId="1" r:id="Rb34d6f3f40ba4d0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App_Base" sheetId="2" r:id="Rd5d1cbf8316f42fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campanha_Checklist" sheetId="3" r:id="R189d1b971525438c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protagonistas_Controle" sheetId="4" r:id="R7468820385a74c91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPCs_Mobs" sheetId="5" r:id="R87ae2d430e344a69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses_Rituais" sheetId="6" r:id="R37f1892c2eb0417d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biomas_Mapas" sheetId="7" r:id="Rc96134a8368642d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio_VFX" sheetId="8" r:id="R896d91e797c949b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Painel" sheetId="9" r:id="Rf55c6bbd54c542df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="10" r:id="R58b61ee621114ec2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="11" r:id="R3f6254925d37490d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Divergencias" sheetId="12" r:id="R3b47fdd91dbb4033"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core_vs_Pack" sheetId="13" r:id="Rbd3e1943f7b64153"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MUN_Assets" sheetId="14" r:id="Ra00633e989694bc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peso_Assets" sheetId="15" r:id="Rfd90d8ab996743d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Teste" sheetId="16" r:id="Rbef9b707970244e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personagens_Campanha" sheetId="17" r:id="R0807bcdac31940ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC_Mecanicas" sheetId="18" r:id="R56c7036a91754057"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protagonistas" sheetId="19" r:id="Raea1db5902e44f9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses_Fases" sheetId="20" r:id="R5d1b8e13e1764f34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Faccoes" sheetId="21" r:id="R8f646d1ba6da41c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mundo_Biomas" sheetId="22" r:id="Rfd64d44fd42b420c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conteudo_Futuro" sheetId="23" r:id="R919bced9a4f2483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controle" sheetId="1" r:id="R58a2119c761e4235"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App_Base" sheetId="2" r:id="Red6cffb8da3d4279"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campanha_Checklist" sheetId="3" r:id="R15b24491e4104d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protagonistas_Controle" sheetId="4" r:id="Rc9e73734459045c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPCs_Mobs" sheetId="5" r:id="R893fe97797be4bcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses_Rituais" sheetId="6" r:id="R60e98b7f71ee4700"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biomas_Mapas" sheetId="7" r:id="R45b55c9698924254"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio_VFX" sheetId="8" r:id="Rd157a6646fec4ee1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Painel" sheetId="9" r:id="Rdc71ff5019954454"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="10" r:id="Re8513a79b845476c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="11" r:id="Rd679f8db85f6424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Divergencias" sheetId="12" r:id="R07c9ecfa66c64e6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core_vs_Pack" sheetId="13" r:id="Ra2ae65209c0e4241"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MUN_Assets" sheetId="14" r:id="R38d78982a02b43ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peso_Assets" sheetId="15" r:id="R0b80300a22d2423b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Teste" sheetId="16" r:id="R9ca3b4442e864bf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personagens_Campanha" sheetId="17" r:id="R5447a86c28034918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC_Mecanicas" sheetId="18" r:id="R4cf3f64ea6504687"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protagonistas" sheetId="19" r:id="Rb131b8b91eed4ab9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses_Fases" sheetId="20" r:id="R2ca8062185804edb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Faccoes" sheetId="21" r:id="Re977664bb8ab4c3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mundo_Biomas" sheetId="22" r:id="R792eab5ec442457b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conteudo_Futuro" sheetId="23" r:id="R533527ea84b3477e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -138,7 +138,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="16">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -215,6 +215,81 @@
         <x:fgColor rgb="FFF7C1C1"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFE7A8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFCFEAD6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7C1C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFE7A8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFCFEAD6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7C1C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFE7A8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFCFEAD6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7C1C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFE7A8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFCFEAD6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7C1C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFE7A8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFCFEAD6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7C1C1"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="4">
     <x:border/>
@@ -264,7 +339,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="49">
+  <x:cellXfs count="92">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -404,6 +479,133 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="20" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="25" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="29" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="29" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1279,7 +1481,7 @@
         </x:is>
       </x:c>
       <x:c r="D14" s="36" t="str">
-        <x:v>Alpha.90 promovida: mapas, recovery e Dia/Noite fechados. Livro, MSC e VFX seguem como frentes separadas.</x:v>
+        <x:v>Alpha.91 promovida: mapas, recovery, Dia/Noite e livros fechados tecnicamente. MSC e VFX seguem como frentes separadas.</x:v>
       </x:c>
       <x:c r="E14" s="8" t="inlineStr">
         <x:is>
@@ -1474,10 +1676,8 @@
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="G23" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Combat V2 e a fonte ativa para CA, Bloqueio, Esquiva, critico, manobras, escala de mobs e simulacao; a correcao canonica de 2026-07-13 tornou Esquiva fixa, mas runtime/Livros aguardam o checkmate da matematica.</x:t>
-        </x:is>
+      <x:c r="G23" s="8" t="str">
+        <x:v>Combat V2 e a fonte ativa para CA, Bloqueio, Esquiva, critico, manobras, escala de mobs e simulacao; FUSHI_COMBAT_V2.md prevalece sobre regra V1 conflitante; qualquer ajuste numerico segue aprovado pelo Mestre e playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1508,11 +1708,9 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="28">
-      <x:c r="G28" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Combat V2 e a fonte ativa para CA, Bloqueio, Esquiva, critico, manobras, escala de mobs e simulacao; FUSHI_COMBAT_V2.md prevalece sobre regra V1 conflitante.</x:t>
-        </x:is>
+    <x:row r="28" ht="54" customHeight="1">
+      <x:c r="G28" s="36" t="str">
+        <x:v>Alpha.91: livros nascem dos JSONs; contagens e paginas sao derivadas; auditoria reprova rotulos editoriais crus; release real 0.1.0-alpha.91.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1526,6 +1724,9 @@
       <x:c r="G30" s="37" t="str">
         <x:v>Alpha.90: preservar a ultima superficie decodificada; Ctrl+A nao troca estado; Relogio MUN e fonte de Dia/Noite; so Mestre edita luzes.</x:v>
       </x:c>
+    </x:row>
+    <x:row r="31" ht="18" customHeight="1">
+      <x:c r="G31" s="37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1560,8 +1761,8 @@
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd43afade6c34567"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf10efd0c1d384c9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re69556f1f0f44edd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R662adc429a554e0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1577,7 +1778,7 @@
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
       <x:c r="A1" s="1" t="str">
-        <x:v>FUSHI App Readiness - Alpha.90</x:v>
+        <x:v>FUSHI App Readiness - Alpha.91</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="19" customHeight="1">
@@ -1639,7 +1840,7 @@
       <x:c r="B7" s="8" t="n">
         <x:v>4422.7</x:v>
       </x:c>
-      <x:c r="C7" s="39" t="str">
+      <x:c r="C7" s="85" t="str">
         <x:v>Pack atual; alvo de otimizacao</x:v>
       </x:c>
     </x:row>
@@ -1668,7 +1869,7 @@
         <x:v>349.2</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
-        <x:v>Core alpha.90 validado</x:v>
+        <x:v>Core alpha.91 validado</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1793,12 +1994,12 @@
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
       <x:c r="A18" s="40" t="str">
-        <x:v>Gate alpha.90</x:v>
-      </x:c>
-      <x:c r="B18" s="42" t="n">
+        <x:v>Gate alpha.91</x:v>
+      </x:c>
+      <x:c r="B18" s="87" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C18" s="42" t="str">
+      <x:c r="C18" s="87" t="str">
         <x:v>12/12 smokes profundos no release real</x:v>
       </x:c>
     </x:row>
@@ -1806,11 +2007,22 @@
       <x:c r="A19" s="40" t="str">
         <x:v>Dia/Noite</x:v>
       </x:c>
-      <x:c r="B19" s="42" t="str">
+      <x:c r="B19" s="87" t="str">
         <x:v>OK tecnico</x:v>
       </x:c>
-      <x:c r="C19" s="42" t="str">
+      <x:c r="C19" s="87" t="str">
         <x:v>Mestre edita; Jogador recebe o visual</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="30" customHeight="1">
+      <x:c r="A20" s="40" t="str">
+        <x:v>Livros</x:v>
+      </x:c>
+      <x:c r="B20" s="87" t="str">
+        <x:v>OK tecnico</x:v>
+      </x:c>
+      <x:c r="C20" s="87" t="str">
+        <x:v>16/19 capitulos; PDFs 28/392; sigilo e auditoria visual aprovados</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1820,7 +2032,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3af52b1e2f284ec0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5752b32a315c4d9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2208,7 +2420,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R743b760dda6b4f7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dc99cc3aa9e4b72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2578,7 +2790,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2bbc72c82d74854"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R544027cb9c32488b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2904,7 +3116,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2568b769228d4220"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd632f1c039fa423c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9498,7 +9710,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf16d7fd543bb4820"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R307854ca5e2d46b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12054,7 +12266,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2444f06047844b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14141bea2f654d6b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12080,7 +12292,7 @@
     </x:row>
     <x:row r="2" ht="19" customHeight="1">
       <x:c r="A2" s="2" t="str">
-        <x:v>Gate obrigatorio da alpha.90 e de qualquer build futura que toque multiplayer, ficha, combate, cena ou eventos.</x:v>
+        <x:v>Gate obrigatorio da alpha.91 e de qualquer build futura que toque multiplayer, ficha, combate, cena, livros ou eventos.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -12596,7 +12808,7 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
-      <x:c r="A20" s="45" t="str">
+      <x:c r="A20" s="89" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="B20" s="40" t="str">
@@ -12611,12 +12823,12 @@
       <x:c r="E20" s="40" t="str">
         <x:v>Smoke interludios + release real</x:v>
       </x:c>
-      <x:c r="F20" s="42" t="str">
-        <x:v>OK automatizado alpha.90</x:v>
+      <x:c r="F20" s="87" t="str">
+        <x:v>OK automatizado alpha.91</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
-      <x:c r="A21" s="45" t="str">
+      <x:c r="A21" s="89" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="B21" s="40" t="str">
@@ -12631,12 +12843,12 @@
       <x:c r="E21" s="40" t="str">
         <x:v>Smoke lighting + multiplayer + deep</x:v>
       </x:c>
-      <x:c r="F21" s="48" t="str">
-        <x:v>OK tecnico alpha.90; teste fisico recomendado</x:v>
+      <x:c r="F21" s="91" t="str">
+        <x:v>OK tecnico alpha.90; alpha.91 revalidado; teste fisico recomendado</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
-      <x:c r="A22" s="45" t="str">
+      <x:c r="A22" s="89" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="B22" s="40" t="str">
@@ -12651,12 +12863,12 @@
       <x:c r="E22" s="40" t="str">
         <x:v>12 smokes empacotados + release real</x:v>
       </x:c>
-      <x:c r="F22" s="42" t="str">
-        <x:v>OK automatizado alpha.90</x:v>
+      <x:c r="F22" s="87" t="str">
+        <x:v>OK automatizado alpha.91</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
-      <x:c r="A23" s="48" t="str">
+      <x:c r="A23" s="91" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="B23" s="40" t="str">
@@ -12671,8 +12883,48 @@
       <x:c r="E23" s="40" t="str">
         <x:v>npm audit --omit=dev + bundle:audit</x:v>
       </x:c>
-      <x:c r="F23" s="48" t="str">
+      <x:c r="F23" s="91" t="str">
         <x:v>ATENCAO - divida registrada</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="54" customHeight="1">
+      <x:c r="A24" s="89" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="B24" s="40" t="str">
+        <x:v>Livros e sigilo</x:v>
+      </x:c>
+      <x:c r="C24" s="40" t="str">
+        <x:v>Abrir o Livro do Jogador e o do Mestre no executavel e pesquisar uma regra publica.</x:v>
+      </x:c>
+      <x:c r="D24" s="40" t="str">
+        <x:v>Jogador tem somente regra publica; Mestre acessa compendio; capitulos e PDFs batem com a fonte.</x:v>
+      </x:c>
+      <x:c r="E24" s="40" t="str">
+        <x:v>books:build + books:audit + smoke:rulebooks:release</x:v>
+      </x:c>
+      <x:c r="F24" s="87" t="str">
+        <x:v>OK automatizado alpha.91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="54" customHeight="1">
+      <x:c r="A25" s="89" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="B25" s="40" t="str">
+        <x:v>Multiplayer soak</x:v>
+      </x:c>
+      <x:c r="C25" s="40" t="str">
+        <x:v>Repetir entrada, sair para Fluxo/Livro, voltar, editar ficha, rolar e reconectar em cinco instancias.</x:v>
+      </x:c>
+      <x:c r="D25" s="40" t="str">
+        <x:v>Nao volta para pending na mesma instancia; dados, ficha, EVE e privacidade permanecem consistentes.</x:v>
+      </x:c>
+      <x:c r="E25" s="40" t="str">
+        <x:v>smoke:multiplayer + smoke:multiplayer:soak</x:v>
+      </x:c>
+      <x:c r="F25" s="91" t="str">
+        <x:v>OK automatizado alpha.91; teste fisico recomendado</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12682,7 +12934,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83a8e4ff54394488"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a19763e8f1446e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16198,7 +16450,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9716f0582c774bae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ca404fa13324bdb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22536,7 +22788,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R306e818c55334441"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R875ed12be63e4bfc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23098,7 +23350,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2acae17d0c27426e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f1d7d12ce4d41a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23194,7 +23446,7 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
-      <x:c r="A6" s="42" t="str">
+      <x:c r="A6" s="87" t="str">
         <x:v>OK</x:v>
       </x:c>
       <x:c r="B6" s="27" t="str">
@@ -23207,7 +23459,7 @@
         <x:v>Entrar como Mestre, mapa e tokens aparecem, sem readiness preso; Ctrl+A recupera apenas a arte visual sem trocar mapa, tokens, camera ou sessao.</x:v>
       </x:c>
       <x:c r="E6" s="27" t="str">
-        <x:v>Alpha.90: smoke:ui e smoke:release aprovados; 79 amostras, 0 quadros vazios e Ctrl+A preservando mapa, tokens e sessao.</x:v>
+        <x:v>Alpha.91: smoke:ui, smoke:release e smoke:release:deep aprovados; recuperacao visual preservando mapa, tokens e sessao.</x:v>
       </x:c>
       <x:c r="F6" s="27" t="str">
         <x:v>Playtest fisico em dois PCs com troca repetida; Ctrl+A e apenas recuperacao do renderer.</x:v>
@@ -23502,7 +23754,7 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
-      <x:c r="A16" s="42" t="str">
+      <x:c r="A16" s="87" t="str">
         <x:v>OK</x:v>
       </x:c>
       <x:c r="B16" s="27" t="str">
@@ -23515,7 +23767,7 @@
         <x:v>Abrir mapa nao fica branco/preto; interludio tem thumb e fallback coerente.</x:v>
       </x:c>
       <x:c r="E16" s="27" t="str">
-        <x:v>Alpha.90: 121/121 fontes validas, 0 thumbs vazias, 0 quadros vazios nos ciclos e 0 falhas de rede.</x:v>
+        <x:v>Alpha.91: 121/121 fontes validas, 0 thumbs vazias, 0 quadros vazios nos ciclos e 0 falhas de rede.</x:v>
       </x:c>
       <x:c r="F16" s="27" t="str">
         <x:v>Revisao artistica por cena; manter auditoria semantica antes de cada release.</x:v>
@@ -23554,7 +23806,7 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
-      <x:c r="A18" s="42" t="str">
+      <x:c r="A18" s="87" t="str">
         <x:v>OK</x:v>
       </x:c>
       <x:c r="B18" s="27" t="str">
@@ -23567,42 +23819,30 @@
         <x:v>release/win-unpacked abre e os smokes rodam isolados.</x:v>
       </x:c>
       <x:c r="E18" s="27" t="str">
-        <x:v>Alpha.90: build, lint, UI, multiplayer, release, lighting, interludios, performance e deep 12/12 aprovados.</x:v>
+        <x:v>Alpha.91: build, lint, UI, multiplayer, soak 5/5, release e deep 12/12 aprovados; executavel versionado 0.1.0-alpha.91.</x:v>
       </x:c>
       <x:c r="F18" s="27" t="str">
         <x:v>Fechar o executavel oficial antes de empacotar e repetir o gate especifico da area.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B19" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Livros</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Livro do Jogador e Livro do Mestre</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Jogador consulta regras publicas no Fluxo e na Mesa sem ver reencarnacao/progressao oculta; Mestre consulta escudo e compendio real; PDFs passam auditoria visual e de sigilo.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E19" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Combat V2: 15 capitulos publicos, 18 capitulos do Mestre, PDF Jogador 23 paginas, PDF Mestre 363 paginas; auditoria visual, sigilo e bordas aprovada.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Atualizar src/data/rulebook a cada decisao aprovada; rodar books:build, books:audit e smoke:rulebooks:release.</x:t>
-        </x:is>
+    <x:row r="19" ht="54" customHeight="1">
+      <x:c r="A19" s="87" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="B19" s="27" t="str">
+        <x:v>Livros</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="str">
+        <x:v>Livro do Jogador e Livro do Mestre</x:v>
+      </x:c>
+      <x:c r="D19" s="27" t="str">
+        <x:v>Fonte unica em src/data/rulebook; Jogador sem segredos; Mestre com compendio completo.</x:v>
+      </x:c>
+      <x:c r="E19" s="27" t="str">
+        <x:v>Alpha.91: 16 capitulos publicos, 19 do Mestre, PDFs 28/392, bibliografia 17; smoke e auditoria visual aprovados.</x:v>
+      </x:c>
+      <x:c r="F19" s="27" t="str">
+        <x:v>Manter books:build, books:audit e smoke:rulebooks:release a cada mudanca editorial.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -23734,7 +23974,7 @@
       </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
-      <x:c r="A24" s="42" t="str">
+      <x:c r="A24" s="87" t="str">
         <x:v>OK tecnico</x:v>
       </x:c>
       <x:c r="B24" s="40" t="str">
@@ -23747,11 +23987,39 @@
         <x:v>Relogio MUN alterna Dia/Noite; Mestre controla lanterna e ate 24 pontos; Jogador ve sem controles.</x:v>
       </x:c>
       <x:c r="E24" s="40" t="str">
-        <x:v>Alpha.90: smoke:lighting isolado e dentro do deep 12/12; multiplayer, release e perf aprovados.</x:v>
+        <x:v>Alpha.90: smoke:lighting isolado e dentro do deep 12/12; alpha.91 revalidou o fluxo empacotado.</x:v>
       </x:c>
       <x:c r="F24" s="40" t="str">
         <x:v>Playtest fisico com noite, cursor, ponto fixo, Ctrl+T, OFF/ON e troca de mapa.</x:v>
       </x:c>
+    </x:row>
+    <x:row r="25" ht="54" customHeight="1">
+      <x:c r="A25" s="87" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="B25" s="40" t="str">
+        <x:v>Multiplayer</x:v>
+      </x:c>
+      <x:c r="C25" s="40" t="str">
+        <x:v>Multiplayer soak</x:v>
+      </x:c>
+      <x:c r="D25" s="40" t="str">
+        <x:v>Aceite unico por instancia, ficha nos dois sentidos, ACK/idempotencia e privacidade preservados.</x:v>
+      </x:c>
+      <x:c r="E25" s="40" t="str">
+        <x:v>Alpha.91: smoke:multiplayer e soak 5/5 loops aprovados; media 1842 ms.</x:v>
+      </x:c>
+      <x:c r="F25" s="40" t="str">
+        <x:v>Revalidar fisicamente em dois computadores antes de uma sessao.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="18" customHeight="1">
+      <x:c r="A26" s="80"/>
+      <x:c r="B26" s="40"/>
+      <x:c r="C26" s="40"/>
+      <x:c r="D26" s="40"/>
+      <x:c r="E26" s="40"/>
+      <x:c r="F26" s="40"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -23760,7 +24028,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4b43c6994a84ba7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51b0779d00d049c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24889,7 +25157,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02079c2e6a3741a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6253acb6c174a60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25319,7 +25587,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f17c067af8b41d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06fc73ddaea743f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25995,7 +26263,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R561441f1237241be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ea8992839d64520"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26293,7 +26561,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14ab59975332486d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re98b01a96f114881"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26573,7 +26841,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7848778f884441e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3d9f9e06bac4f96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27027,7 +27295,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf25996534c6d4ce4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0e76549441646e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29920,7 +30188,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d525b10de6144cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc445922f9cef41ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30968,7 +31236,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd9e51fb5bdb48b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb39148c193e54650"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31509,7 +31777,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R465feb5a9ec74e43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ba50808049c45c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31931,7 +32199,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43c6efa87d9b4b20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ea62b6ab5624694"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32352,7 +32620,7 @@
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e917587842f451f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93ad9493b7df40a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
+++ b/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>349.2</v>
+        <v>349.4</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>349.2 MiB</t>
+          <t>349.4 MiB</t>
         </is>
       </c>
     </row>
@@ -31819,7 +31819,7 @@
     <hyperlink ref="C13" location="'Conteudo_Futuro'!A1" display="5 vazios"/>
     <hyperlink ref="E13" location="'Conteudo_Futuro'!A1" display="0 pronto"/>
     <hyperlink ref="G13" location="'Divergencias'!A1" display="6 pontos"/>
-    <hyperlink ref="I13" location="'Core_vs_Pack'!A1" display="349.2 MiB"/>
+    <hyperlink ref="I13" location="'Core_vs_Pack'!A1" display="349.4 MiB"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
+++ b/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
@@ -643,8 +643,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="AppBaseChecklistTable" displayName="AppBaseChecklistTable" ref="A4:F26" headerRowCount="1">
-  <autoFilter ref="A4:F26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="AppBaseChecklistTable" displayName="AppBaseChecklistTable" ref="A4:F28" headerRowCount="1">
+  <autoFilter ref="A4:F28"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Area"/>
@@ -1462,7 +1462,7 @@
     <row r="31">
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Alpha.92: Cronicas da Ilha sao publicas e o Livro da Historia e exclusivo do Mestre; VFX sao apresentacoes efemeras com vfxExpiresAt, sem replay no reconnect; MSC fica bloqueado ate o teste fisico.</t>
+          <t>Alpha.92: Cronicas da Ilha sao publicas e o Livro da Historia e exclusivo do Mestre; VFX sao apresentacoes efemeras com vfxExpiresAt, sem replay no reconnect; MSC usa uma biblioteca unica, com pastas persistentes, capas opcionais e estado sanitizado no multiplayer.</t>
         </is>
       </c>
     </row>
@@ -22504,7 +22504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -23010,66 +23010,66 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>FOCO</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Livros</t>
+          <t>Dependencias</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Livro do Jogador e Livro do Mestre</t>
+          <t>Alertas npm audit</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Jogador consulta regras publicas no Fluxo e na Mesa sem ver reencarnacao/progressao oculta; Mestre consulta escudo e compendio real; PDFs passam auditoria visual e de sigilo.</t>
+          <t>Nenhuma correcao de dependencia pode regredir launcher, navegacao, Mesa ou multiplayer; alvo final e zero alerta alto aplicavel ao runtime.</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Combat V2: 16 capitulos publicos, 19 capitulos do Mestre, PDF Jogador 28 paginas, PDF Mestre 392 paginas; auditoria visual, sigilo e bordas aprovada.</t>
+          <t>01/08/2026: 0 criticas, 0 moderadas e 3 altas residuais; brace-expansion e transitivo, react-router-dom e direto.</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Atualizar src/data/rulebook a cada decisao aprovada; rodar books:build, books:audit e smoke:rulebooks:release.</t>
+          <t>Testar atualizacao em branch dedicada com build, smoke:ui, smoke:multiplayer e smoke:release; nao aplicar npm audit fix automatico na build de sessao.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>OK tecnico</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Livros</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Cronica publica e Livro da Historia</t>
+          <t>Livro do Jogador e Livro do Mestre</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Jogador ve somente acontecimentos liberados; Mestre ve continuidade, segredos e lacunas; Sessao 4 permanece pendente ate log real.</t>
+          <t>Jogador consulta regras publicas no Fluxo e na Mesa sem ver reencarnacao/progressao oculta; Mestre consulta escudo e compendio real; PDFs passam auditoria visual e de sigilo.</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Alpha.92: dois JSONs separados, PDFs publicos e confidenciais auditados; smoke:history-vfx confirmou seis secoes publicas, oito do Mestre e bloqueio de termos proibidos.</t>
+          <t>Combat V2: 16 capitulos publicos, 19 capitulos do Mestre, PDF Jogador 28 paginas, PDF Mestre 392 paginas; auditoria visual, sigilo e bordas aprovada.</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Depois da proxima sessao, atualizar primeiro o log real e somente entao regenerar os dois volumes.</t>
+          <t>Atualizar src/data/rulebook a cada decisao aprovada; rodar books:build, books:audit e smoke:rulebooks:release.</t>
         </is>
       </c>
     </row>
@@ -23081,155 +23081,155 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
+          <t>Historia</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Cronica publica e Livro da Historia</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Jogador ve somente acontecimentos liberados; Mestre ve continuidade, segredos e lacunas; Sessao 4 permanece pendente ate log real.</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Alpha.92: dois JSONs separados, PDFs publicos e confidenciais auditados; smoke:history-vfx confirmou seis secoes publicas, oito do Mestre e bloqueio de termos proibidos.</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Depois da proxima sessao, atualizar primeiro o log real e somente entao regenerar os dois volumes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>OK tecnico</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
           <t>VFX</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Catalogo VFX efemero</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Preview local nao vaza; broadcast do Mestre aparece uma vez para a mesa; clear/expiracao impedem replay em reconnect e troca de mapa.</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Alpha.92: catalogo declarativo com 10 presets, vfxExpiresAt obrigatorio e filtro de pulso antigo; smoke:history-vfx e gate empacotado dedicados.</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Playtest fisico de um preview, um broadcast e um reconnect; MSC continua bloqueado ate esse teste.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Playtest fisico de um preview, um broadcast e um reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>OK tecnico</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Biblioteca MSC de sessao</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Pastas permanecem visiveis; busca, favoritos, tocando agora, volume, play/pause/stop, criar, editar, excluir e capas opcionais sobrevivem ao fechamento; metadados chegam ao Jogador sem vazar controles do Mestre.</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Alpha.92: interface visual em grade validada no release empacotado; smoke:release edita nome/capa e reabre a biblioteca; smoke:multiplayer protege custom track, previewImage e override de faixa nativa.</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Playtest fisico Mestre/Jogador de volume, troca de pasta, edicao de capa e retorno a Mesa; depois catalogar temas por cena/personagem sem mover os arquivos atuais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>FOCO</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Combate</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Combat V2 - defesa, critico e turnos</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>CA e passiva; Bloqueio usa Fortitude (0/5/10/15); Esquiva fixa usa CA atual + AGI + Reflexos como Reacao; critico dobra apenas dados; turnos mostram Principal, Curta, Movimento, Reacao e manobras.</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Alpha.88: 56 fichas Combat V2; fluxo visual ficha -&gt; Dados de Combate -&gt; dado -&gt; Resolver -&gt; confirmacao; recibo privado, impacto, marca e queda protegidos por smokes runtime, UI e multiplayer.</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>Playtest fisico curto Mestre/Jogador para confirmar leitura e ritmo; manter Veyra e demais lacunas de conteudo como alerta ate revisao canonica do Mestre.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>FOCO</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Builds</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Catalogo, raridades e vinculo BUI</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>48 itens, cinco raridades, conjuntos de NPC e vinculo canonico funcionam sem alterar lore ou aceitar sobrescrita do Jogador.</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Baseline canonico aprovado por smoke:builds: 48 itens, 240 raridades e 41 conjuntos 8/8. Alpha.87 separa valor base do efetivo: editar base reaplica o total da build e remover item restaura a base sem residuo; smoke:ui e multiplayer protegem o contrato.</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>Em teste real: editar a Vida base de Connor para 20, confirmar 34 com Build +14, remover a build e confirmar retorno a 20. Ajustar numeros somente com evidencia de playtest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Eventos</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Hub EVE e ciclo de vida</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Mestre ativa dois ou mais eventos, desativa cada um isoladamente e a Mesa volta ao estado-base sem apagar progresso.</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>Treino Inicial e Sorteio Raridade Build passaram em build, smoke:events, smoke:training:ui, smoke:multiplayer, smoke:release e smoke:release:deep 11/11; campos privados foram removidos do payload do Jogador e a revelacao agora fecha por clique sem alterar ficha/EVE.</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Manter em teste real; todo evento novo deve seguir FUSHI_EVENT_SYSTEM_V1 e ganhar smoke proprio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>OK tecnico</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Dia/Noite e iluminacao</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Relogio MUN alterna Dia/Noite; Mestre controla pontos e lanterna; Jogador ve o resultado sem controles; estado persiste por troca de mapa e reconexao.</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>Alpha.90: smoke:lighting isolado e dentro de smoke:release:deep; 12/12 deep, smoke:multiplayer, smoke:release e perf:release aprovados; limite de 24 luzes por cena.</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Playtest fisico Mestre/Jogador com noite, cursor, ponto fixo, Ctrl+T, OFF/ON e troca de mapa.</t>
         </is>
       </c>
     </row>
@@ -23241,25 +23241,89 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
+          <t>Eventos</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Hub EVE e ciclo de vida</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Mestre ativa dois ou mais eventos, desativa cada um isoladamente e a Mesa volta ao estado-base sem apagar progresso.</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Treino Inicial e Sorteio Raridade Build passaram em build, smoke:events, smoke:training:ui, smoke:multiplayer, smoke:release e smoke:release:deep 11/11; campos privados foram removidos do payload do Jogador e a revelacao agora fecha por clique sem alterar ficha/EVE.</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Manter em teste real; todo evento novo deve seguir FUSHI_EVENT_SYSTEM_V1 e ganhar smoke proprio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>OK tecnico</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Dia/Noite e iluminacao</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Relogio MUN alterna Dia/Noite; Mestre controla pontos e lanterna; Jogador ve o resultado sem controles; estado persiste por troca de mapa e reconexao.</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Alpha.90: smoke:lighting isolado e dentro de smoke:release:deep; 12/12 deep, smoke:multiplayer, smoke:release e perf:release aprovados; limite de 24 luzes por cena.</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Playtest fisico Mestre/Jogador com noite, cursor, ponto fixo, Ctrl+T, OFF/ON e troca de mapa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
           <t>Treinamento</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Circuito do Centro no Campo de Treinamento</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Mestre ativa/desativa pelo EVE ou MUN; cinco jogadores veem quests e progresso; somente Mestre ve DT e aplica Marcas, Contratempos e Segundo Sino.</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>smoke:training, smoke:training:ui e smoke:multiplayer aprovados; desativacao remove o painel em Mestre/Jogador, preserva a Marca e permite retomar.</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>Teste real na proxima sessao; refinamento narrativo e habilidades continuam dependendo de aprovacao do Mestre.</t>
         </is>
@@ -25993,7 +26057,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Preencher depois do protocolo de pack/audio.</t>
+          <t>Usar a biblioteca MSC ja estabilizada para catalogar por cena, bioma, personagem, combate, tensao, descanso, boss e interludio; nao baixar mais assets antes dessa curadoria.</t>
         </is>
       </c>
     </row>

--- a/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
+++ b/06_TOOLS/fushi-tabletop/docs/planejamento/FUSHI_App_Readiness_Alpha84.xlsx
@@ -2,29 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controle" sheetId="1" r:id="R8c97f4f42d6848ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App_Base" sheetId="2" r:id="R190694e9ba31403d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campanha_Checklist" sheetId="3" r:id="R4f1209d4accc4a93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protagonistas_Controle" sheetId="4" r:id="R3ffe7627d42d4dbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPCs_Mobs" sheetId="5" r:id="Rcab0e9c3cd2f4dd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses_Rituais" sheetId="6" r:id="Rc0dce3dfdf4d4a6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biomas_Mapas" sheetId="7" r:id="Rdb82a1c5a50340b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio_VFX" sheetId="8" r:id="Rc39683db6853413d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Painel" sheetId="9" r:id="R04dbdc13bd994b5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="10" r:id="Ref169e775cfd4fb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="11" r:id="Rc398832d7cb741f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Divergencias" sheetId="12" r:id="R9e0c544915ec40a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core_vs_Pack" sheetId="13" r:id="R4792de19bd9844b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MUN_Assets" sheetId="14" r:id="R2ad7c5fdec6d4d79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peso_Assets" sheetId="15" r:id="Rc461071add5c445a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Teste" sheetId="16" r:id="R4c1af7530cb2484f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personagens_Campanha" sheetId="17" r:id="Rb37f5b2402534614"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC_Mecanicas" sheetId="18" r:id="R067fa5c1be634bd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protagonistas" sheetId="19" r:id="Rae309086ee0741bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses_Fases" sheetId="20" r:id="R9c96fbf15f724c84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Faccoes" sheetId="21" r:id="Rd61546b555914734"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mundo_Biomas" sheetId="22" r:id="R8d1c995c557f4c25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conteudo_Futuro" sheetId="23" r:id="Rbe51ed96b30f496e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controle" sheetId="1" r:id="Rf1f6ff680012406c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App_Base" sheetId="2" r:id="Rd30c8f37080641ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campanha_Checklist" sheetId="3" r:id="R818dc156d25f4765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protagonistas_Controle" sheetId="4" r:id="R1eb345a0b4f1493d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPCs_Mobs" sheetId="5" r:id="Ra5376695aa8849e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses_Rituais" sheetId="6" r:id="R2562a07a13ec4a91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biomas_Mapas" sheetId="7" r:id="Rd39f9b188d2d48f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio_VFX" sheetId="8" r:id="R1464275ea6564dcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Painel" sheetId="9" r:id="R86b35289ad02429d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="10" r:id="R04c33f35425c4698"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="11" r:id="R390580daa38849b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Divergencias" sheetId="12" r:id="Rebcad0e6b98f4bf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core_vs_Pack" sheetId="13" r:id="R9a18642bb80c4b08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MUN_Assets" sheetId="14" r:id="R2875ce9fa7b643f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peso_Assets" sheetId="15" r:id="R3d8ec56f5d9c40c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Teste" sheetId="16" r:id="R6f96dc89212648f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personagens_Campanha" sheetId="17" r:id="R5599e01aafad42a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC_Mecanicas" sheetId="18" r:id="R16b90056548642b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protagonistas" sheetId="19" r:id="R8779967d7e774282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bosses_Fases" sheetId="20" r:id="R5a0fc6cb6f804602"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Faccoes" sheetId="21" r:id="R4d5377a754a8434b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mundo_Biomas" sheetId="22" r:id="R9f40bc1c76c84036"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conteudo_Futuro" sheetId="23" r:id="Rb79af457a4b74a80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -35,7 +35,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="16">
+  <x:fonts count="20">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -108,8 +108,31 @@
       <x:sz val="14"/>
       <x:color rgb="FF7F1D1D"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1D2624"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF135D36"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1D2624"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF8B1E1E"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="20">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -156,6 +179,56 @@
         <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFCFEAD6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFCFEAD6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7FAF8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF6C7C7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFCFEAD6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7FAF8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF6C7C7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFCFEAD6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7FAF8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF6C7C7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="3">
     <x:border/>
@@ -191,7 +264,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="70">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -240,6 +313,155 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1371,6 +1593,11 @@
         <x:v>Alpha.92: Cronicas da Ilha sao publicas e o Livro da Historia e exclusivo do Mestre; VFX sao apresentacoes efemeras com vfxExpiresAt, sem replay no reconnect; MSC usa uma biblioteca unica, com pastas persistentes, capas opcionais e estado sanitizado no multiplayer; Mapas/interludios, Escudo, OBJ, NPC, BUI, EVE e VFX compartilham o mesmo navegador visual, enquanto visualThumbnails permanece privado no workspace do Mestre.</x:v>
       </x:c>
     </x:row>
+    <x:row r="32" ht="92" customHeight="1">
+      <x:c r="G32" s="25" t="str">
+        <x:v>Alpha.92 estabilidade 08/08: tela branca usa detector por blocos e recuperacao real do renderer; navegadores visuais usam arvore recolhida, scroll independente, Pasta+ funcional, menu de contexto, arraste para ordenar e seletores neutros. A rodada nao altera lore, protocolo multiplayer nem a regra de movimento de tokens.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A4:B4"/>
@@ -1404,8 +1631,8 @@
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Readb8e65f8f84eca"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40f5d2672cbb434e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R952780ffe3d74ac5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94dd44db5d1846e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1425,10 +1652,8 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="19" customHeight="1">
-      <x:c r="A2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fonte unica de verdade para preservar a mesa estavel e planejar conteudo.</x:t>
-        </x:is>
+      <x:c r="A2" s="2" t="str">
+        <x:v>Fonte unica de verdade para preservar a mesa estavel e planejar conteudo. Atualizado em 2026-08-08.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1641,6 +1866,39 @@
         <x:is>
           <x:t xml:space="preserve">Conteudo futuro</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="28" customHeight="1">
+      <x:c r="A18" s="20" t="str">
+        <x:v>Gate release deep</x:v>
+      </x:c>
+      <x:c r="B18" s="60" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="str">
+        <x:v>12/12 no release real em 08/08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="28" customHeight="1">
+      <x:c r="A19" s="20" t="str">
+        <x:v>Recuperacao branca</x:v>
+      </x:c>
+      <x:c r="B19" s="60" t="str">
+        <x:v>OK tecnico</x:v>
+      </x:c>
+      <x:c r="C19" s="20" t="str">
+        <x:v>Detector 6x6 + reload real</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="28" customHeight="1">
+      <x:c r="A20" s="20" t="str">
+        <x:v>Navegadores visuais</x:v>
+      </x:c>
+      <x:c r="B20" s="60" t="str">
+        <x:v>OK tecnico</x:v>
+      </x:c>
+      <x:c r="C20" s="20" t="str">
+        <x:v>Arvore, drag e scroll validados</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1650,7 +1908,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R372fff285eac43ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ba97b6fb1b34c47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2038,7 +2296,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd94fd21c309143f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61e79699996a41f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2408,7 +2666,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4e5fdb77aea47ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3fbff24187243c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2734,7 +2992,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfa22e09997f416c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfde4dc53b0b4545"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9328,7 +9586,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ad72a416008474a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1baff79f88f48c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11884,7 +12142,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc47387e5d3ec4247"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbada3cc012d4c0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12425,23 +12683,63 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="str">
+    <x:row r="20" ht="58" customHeight="1">
+      <x:c r="A20" s="69" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="B20" t="str">
+      <x:c r="B20" s="65" t="str">
         <x:v>Bibliotecas visuais e thumbnails</x:v>
       </x:c>
-      <x:c r="C20" t="str">
+      <x:c r="C20" s="65" t="str">
         <x:v>Abrir MAP, Escudo, OBJ, NPC, BUI, EVE e VFX; trocar categorias; no EVE enviar capa, fechar/reabrir e remover.</x:v>
       </x:c>
-      <x:c r="D20" t="str">
+      <x:c r="D20" s="65" t="str">
         <x:v>Cada hub preserva a logica anterior; a capa persiste no Mestre; controles e metadata privados nao vazam ao Jogador.</x:v>
       </x:c>
-      <x:c r="E20" t="str">
+      <x:c r="E20" s="65" t="str">
         <x:v>Smoke UI + multiplayer + release deep</x:v>
       </x:c>
-      <x:c r="F20" t="str">
+      <x:c r="F20" s="60" t="str">
+        <x:v>OK automatizado alpha.92; teste fisico recomendado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="66" customHeight="1">
+      <x:c r="A21" s="69" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="B21" s="65" t="str">
+        <x:v>Recuperacao real da mesa branca</x:v>
+      </x:c>
+      <x:c r="C21" s="65" t="str">
+        <x:v>Forcar a superficie central branca, aguardar a sonda confirmar blocos vazios e pressionar Ctrl+A.</x:v>
+      </x:c>
+      <x:c r="D21" s="65" t="str">
+        <x:v>Nao exibe sucesso antecipado; recarrega o renderer, reconecta o teste e preserva mapa, tokens e sessao.</x:v>
+      </x:c>
+      <x:c r="E21" s="65" t="str">
+        <x:v>Smoke release deep + Electron</x:v>
+      </x:c>
+      <x:c r="F21" s="60" t="str">
+        <x:v>OK automatizado alpha.92; teste fisico recomendado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="78" customHeight="1">
+      <x:c r="A22" s="69" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="B22" s="65" t="str">
+        <x:v>Pastas e navegadores visuais</x:v>
+      </x:c>
+      <x:c r="C22" s="65" t="str">
+        <x:v>Abrir MAP/MSC/NPC; expandir MUN, recolher, criar pasta, renomear pelo contexto, arrastar para reordenar e rolar lateral/conteudo separadamente.</x:v>
+      </x:c>
+      <x:c r="D22" s="65" t="str">
+        <x:v>Filhos so aparecem com o pai aberto; ordem persiste; Pasta+ funciona; os dois scrolls nao se arrastam juntos e nenhuma acao recarrega a mesa.</x:v>
+      </x:c>
+      <x:c r="E22" s="65" t="str">
+        <x:v>Smoke UI + release deep</x:v>
+      </x:c>
+      <x:c r="F22" s="60" t="str">
         <x:v>OK automatizado alpha.92; teste fisico recomendado</x:v>
       </x:c>
     </x:row>
@@ -12452,7 +12750,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07ed89c1afac4e42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd536dc3abca54979"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15968,7 +16266,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05102001b25e4dab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0716c53e1a54c16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22306,7 +22604,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R423b39b32ae54e31"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fccf17a0d8d4f09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22868,7 +23166,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcabdb5a0eb284a25"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R539d5e6eca0449d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22963,36 +23261,32 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="7" t="inlineStr">
+    <x:row r="6" ht="78" customHeight="1">
+      <x:c r="A6" s="61" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">OK</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="8" t="inlineStr">
+      <x:c r="B6" s="62" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Mesa</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" s="8" t="inlineStr">
+      <x:c r="C6" s="62" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Mesa Mestre carrega</x:t>
         </x:is>
       </x:c>
-      <x:c r="D6" s="8" t="inlineStr">
+      <x:c r="D6" s="62" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Entrar como Mestre, mapa e tokens aparecem, sem readiness preso; Ctrl+A recupera apenas a arte visual sem trocar mapa, tokens, camera ou sessao.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E6" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Alpha.90: smoke:ui e smoke:release aprovados; smoke:release:deep mediu 79 amostras, 0 quadros vazios, 11 quadros stale durante a preparacao e confirmou Ctrl+A sem trocar mapa, tokens ou sessao.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Playtest fisico em dois PCs com troca repetida de mapas; usar Ctrl+A apenas como recuperacao de renderer se uma superficie ficar branca.</x:t>
-        </x:is>
+      <x:c r="E6" s="62" t="str">
+        <x:v>Alpha.92 em 08/08: smoke:release:deep passou 12/12. A sonda forcou uma superficie 100% branca, o detector 6x6 confirmou blankTileRatio 1, o renderer recarregou de verdade e mapa, tokens e sessao foram restaurados sem falso positivo.</x:v>
+      </x:c>
+      <x:c r="F6" s="62" t="str">
+        <x:v>Playtest fisico em dois PCs com troca repetida de mapas. Ctrl+A e contingencia; o fluxo normal deve permanecer estavel sem uso do atalho.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -23347,34 +23641,32 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="7" t="inlineStr">
+    <x:row r="18" ht="70" customHeight="1">
+      <x:c r="A18" s="61" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">OK</x:t>
         </x:is>
       </x:c>
-      <x:c r="B18" s="8" t="inlineStr">
+      <x:c r="B18" s="62" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Release</x:t>
         </x:is>
       </x:c>
-      <x:c r="C18" s="8" t="inlineStr">
+      <x:c r="C18" s="62" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Build empacotado real</x:t>
         </x:is>
       </x:c>
-      <x:c r="D18" s="8" t="inlineStr">
+      <x:c r="D18" s="62" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">release/win-unpacked abre e smokes rodam isolados.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E18" s="8" t="str">
-        <x:v>Alpha.92 empacotada novamente em 02/08/2026: build e instalador passaram; smoke:release passou em execucao isolada; release:assets confirmou 349,4 MB core, 50 audios e nenhuma copia publica no ASAR; smoke:release:deep 12/12 passou.</x:v>
-      </x:c>
-      <x:c r="F18" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Nao promover conteudo sem fechar o executavel oficial, rodar smoke:release e o gate especifico da area alterada.</x:t>
-        </x:is>
+      <x:c r="E18" s="62" t="str">
+        <x:v>Alpha.92 empacotada novamente em 08/08/2026. Lint, build, smoke:ui, smoke:multiplayer, smoke:release e smoke:release:deep 12/12 passaram; instaladores offline e web foram regenerados.</x:v>
+      </x:c>
+      <x:c r="F18" s="62" t="str">
+        <x:v>Manter fechamento escopado do executavel, smoke:release e gate profundo antes de promover qualquer mudanca estrutural.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -23697,24 +23989,24 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="29">
-      <x:c r="A29" t="str">
+    <x:row r="29" ht="132" customHeight="1">
+      <x:c r="A29" s="63" t="str">
         <x:v>OK tecnico</x:v>
       </x:c>
-      <x:c r="B29" t="str">
+      <x:c r="B29" s="63" t="str">
         <x:v>Interface</x:v>
       </x:c>
-      <x:c r="C29" t="str">
+      <x:c r="C29" s="63" t="str">
         <x:v>Bibliotecas visuais unificadas</x:v>
       </x:c>
-      <x:c r="D29" t="str">
+      <x:c r="D29" s="63" t="str">
         <x:v>Mapas/interludios, Escudo, OBJ, NPC, BUI, EVE e VFX usam busca, categorias persistentes a esquerda e cards a direita, preservando controles, dados e permissoes de cada hub.</x:v>
       </x:c>
-      <x:c r="E29" t="str">
-        <x:v>Alpha.92: smoke:ui abriu os sete hubs no release e validou upload PNG/JPG/WebP persistente no EVE com reabertura e remocao; thumbnails privadas nao entram no payload do Jogador.</x:v>
-      </x:c>
-      <x:c r="F29" t="str">
-        <x:v>Playtest fisico: alternar pastas, editar uma capa e confirmar que Mestre/Jogador veem apenas o que devem.</x:v>
+      <x:c r="E29" s="63" t="str">
+        <x:v>Alpha.92 em 08/08: MAP/MSC/NPC usam arvore recolhida real, subpastas por expansao, scroll lateral independente, Pasta+ funcional, menu de contexto e reordenacao por arraste. BUI inicia sem ficha escolhida; BUF, TURN, NET e MUN mantiveram a logica com hierarquia visual compacta.</x:v>
+      </x:c>
+      <x:c r="F29" s="63" t="str">
+        <x:v>Playtest fisico: expandir/recolher MUN, arrastar duas pastas, criar/renomear pasta e confirmar que selecionar hubs nao dispara novo carregamento da mesa.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -23724,7 +24016,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R893721ea32c445c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15ab19fa5e73489b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24853,7 +25145,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R598e69f3e77c4313"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf13ae78fae364ed8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25283,7 +25575,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37a49ca3bb214c79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24512572938b47bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25959,7 +26251,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf63ac40b6ad645c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e930359dfb84c89"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26257,7 +26549,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e06390fdbde4143"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15d5e25145034042"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26537,7 +26829,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R140c61e72ad9447a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R731e33a80d3f428c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26991,7 +27283,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b13ce6b880943aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3e1720e84cb4b95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29884,7 +30176,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d7c8e222d7d4a7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72096fe08feb446e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30932,7 +31224,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1b548beddbe4fa2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18e5d02a6c524d8b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31473,7 +31765,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46a505829cea4221"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb35a0f285f0f4e96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31895,7 +32187,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdceb0eb510754711"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20388c088abb4ffc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32316,7 +32608,7 @@
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R723e0acd02044274"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc0dae9a983b4435"/>
   </x:tableParts>
 </x:worksheet>
 </file>